--- a/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
+++ b/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Práctica 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7CAD82CC-3098-4D52-A240-559644177B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3590779-F7A7-4F3E-9859-2D94FC2A9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B0EAA5F-3816-4796-860C-BD0B64EC5768}"/>
   </bookViews>
   <sheets>
     <sheet name="ca_cest_brandi_carlile - copia" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
   <si>
     <t>MIN:</t>
   </si>
@@ -62,6 +75,33 @@
   </si>
   <si>
     <t>Tempo</t>
+  </si>
+  <si>
+    <t>Duda:</t>
+  </si>
+  <si>
+    <t>¿Es normal que los datos de Loudness los estemos trabajando como positivos?</t>
+  </si>
+  <si>
+    <t>¿Cuántas veces repito esto?</t>
+  </si>
+  <si>
+    <t>DC0</t>
+  </si>
+  <si>
+    <t>DC1</t>
+  </si>
+  <si>
+    <t>Distancia aeuclidian: Resta de las coordenadas de ambos puntos en la misma dimensión al cuadrado, sumada a tra´ves de todas las dimensiones en raíz</t>
+  </si>
+  <si>
+    <t>dcmin</t>
+  </si>
+  <si>
+    <t>c0</t>
+  </si>
+  <si>
+    <t>c1</t>
   </si>
 </sst>
 </file>
@@ -545,8 +585,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -922,10 +963,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9653E2FD-8EE4-4C35-A4F1-EC87F3E3C160}">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -977,8 +1034,63 @@
         <f t="shared" si="0"/>
         <v>69.045000000000002</v>
       </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <f>MIN(P5:P55)</f>
+        <v>0</v>
+      </c>
+      <c r="Q1">
+        <f t="shared" ref="Q1:AA1" si="1">MIN(Q5:Q55)</f>
+        <v>0</v>
+      </c>
+      <c r="R1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF1">
+        <f>(SUMPRODUCT(P5:P55,AF5:AF55)+P1)/(AF56+1)</f>
+        <v>0.39292103294304903</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -987,39 +1099,39 @@
         <v>352687</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:M2" si="1">MAX(C5:C55)</f>
+        <f t="shared" ref="C2:M2" si="2">MAX(C5:C55)</f>
         <v>71</v>
       </c>
       <c r="D2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.72599999999999998</v>
       </c>
       <c r="E2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.83899999999999997</v>
       </c>
       <c r="F2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="G2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.0720000000000001</v>
       </c>
       <c r="H2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10299999999999999</v>
       </c>
       <c r="I2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.94199999999999995</v>
       </c>
       <c r="J2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0199999999999997E-2</v>
       </c>
       <c r="K2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.73899999999999999</v>
       </c>
       <c r="L2">
@@ -1027,11 +1139,65 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="M2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>184.21199999999999</v>
       </c>
+      <c r="O2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <f>MAX(P5:P55)</f>
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:AA2" si="3">MAX(Q5:Q55)</f>
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -1068,8 +1234,59 @@
       <c r="M4" t="s">
         <v>13</v>
       </c>
+      <c r="P4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4" t="s">
+        <v>5</v>
+      </c>
+      <c r="T4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>265306</v>
       </c>
@@ -1106,8 +1323,100 @@
       <c r="M5">
         <v>82.766999999999996</v>
       </c>
+      <c r="P5">
+        <f>(B5 - $B$1)/($B$2 - $B$1)</f>
+        <v>0.58359662039485916</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q36" si="4">(C5 - $C$1)/($C$2 - $C$1)</f>
+        <v>0.64516129032258063</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R36" si="5">(D5 - $D$1)/($D$2 - $D$1)</f>
+        <v>0.44081632653061231</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S36" si="6">(E5 - $E$1)/($E$2- $E$1)</f>
+        <v>0.32903565320352585</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T36" si="7">(F5 - $F$1)/($F$2- $F$1)</f>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U36" si="8">(G5 - $G$1)/($G$2- $G$1)</f>
+        <v>0.16196046793061716</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V36" si="9">(H5 - $H$1)/($H$2- $H$1)</f>
+        <v>0.2183462532299742</v>
+      </c>
+      <c r="W5">
+        <f t="shared" ref="W5:W36" si="10">(I5 - $I$1)/($I$2- $I$1)</f>
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ref="X5:X36" si="11">(J5 - $J$1)/($J$2- $J$1)</f>
+        <v>2.1262458471760802E-2</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ref="Y5:Y36" si="12">(K5 - $K$1)/($K$2- $K$1)</f>
+        <v>7.6756912442396311E-2</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" ref="Z5:Z36" si="13">(L5 - $L$1)/($L$2- $L$1)</f>
+        <v>0.1569348904175332</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" ref="AA5:AA36" si="14">(M5 - $M$1)/($M$2- $M$1)</f>
+        <v>0.11914871447550075</v>
+      </c>
+      <c r="AC5">
+        <f>SQRT(
+($P$1 - P5)^2 +
+($Q$1 -Q5)^2 +
+($R$1 - R5)^2 +
+($S$1 - S5)^2 +
+($T$1 - T5)^2 +
+($U$1 - U5)^2 +
+($V$1 - V5)^2 +
+($W$1 - W5)^2 +
+($X$1 - X5)^2 +
+($Y$1 - Y5)^2 +
+($Z$1 - Z5)^2 +
+($AA$1 - AA5)^2)</f>
+        <v>1.645418546063</v>
+      </c>
+      <c r="AD5">
+        <f>SQRT(
+($P$2 - P5)^2 +
+($Q$2 -Q5)^2 +
+($R$2 - R5)^2 +
+($S$2 - S5)^2 +
+($T$2 - T5)^2 +
+($U$2 - U5)^2 +
+($V$2 - V5)^2 +
+($W$2 - W5)^2 +
+($X$2 - X5)^2 +
+($Y$2 - Y5)^2 +
+($Z$2 - Z5)^2 +
+($AA$2 - AA5)^2)</f>
+        <v>2.3972520856897592</v>
+      </c>
+      <c r="AE5">
+        <f>MIN(AC5:AD5)</f>
+        <v>1.645418546063</v>
+      </c>
+      <c r="AF5">
+        <f>IF(AE5=AC5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <f>IF(AE5=AD5,1,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>268653</v>
       </c>
@@ -1144,8 +1453,100 @@
       <c r="M6">
         <v>152.99700000000001</v>
       </c>
+      <c r="P6">
+        <f t="shared" ref="P6:P55" si="15">(B6 - $B$1)/($B$2 - $B$1)</f>
+        <v>0.59954633614014019</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="5"/>
+        <v>0.12448979591836734</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="7"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="8"/>
+        <v>0.962081484469544</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="9"/>
+        <v>0.76485788113695097</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="10"/>
+        <v>0.42255543148827573</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="12"/>
+        <v>7.4740783410138248E-2</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="13"/>
+        <v>0.32490801471764519</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="14"/>
+        <v>0.72895881632759407</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" ref="AC6:AC55" si="16">SQRT(
+($P$1 - P6)^2 +
+($Q$1 -Q6)^2 +
+($R$1 - R6)^2 +
+($S$1 - S6)^2 +
+($T$1 - T6)^2 +
+($U$1 - U6)^2 +
+($V$1 - V6)^2 +
+($W$1 - W6)^2 +
+($X$1 - X6)^2 +
+($Y$1 - Y6)^2 +
+($Z$1 - Z6)^2 +
+($AA$1 - AA6)^2)</f>
+        <v>2.2608861113651288</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" ref="AD6:AD55" si="17">SQRT(
+($P$2 - P6)^2 +
+($Q$2 -Q6)^2 +
+($R$2 - R6)^2 +
+($S$2 - S6)^2 +
+($T$2 - T6)^2 +
+($U$2 - U6)^2 +
+($V$2 - V6)^2 +
+($W$2 - W6)^2 +
+($X$2 - X6)^2 +
+($Y$2 - Y6)^2 +
+($Z$2 - Z6)^2 +
+($AA$2 - AA6)^2)</f>
+        <v>1.9582138924589287</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" ref="AE6:AE55" si="18">MIN(AC6:AD6)</f>
+        <v>1.9582138924589287</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" ref="AF6:AF55" si="19">IF(AE6=AC6,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" ref="AG6:AG55" si="20">IF(AE6=AD6,1,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>231000</v>
       </c>
@@ -1182,8 +1583,76 @@
       <c r="M7">
         <v>172.006</v>
       </c>
+      <c r="P7">
+        <f t="shared" si="15"/>
+        <v>0.42011560803823739</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="5"/>
+        <v>0.54489795918367356</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="6"/>
+        <v>0.84607288514669121</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="8"/>
+        <v>0.64471561113352149</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="10"/>
+        <v>0.21624926888924337</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="11"/>
+        <v>5.8471760797342194E-4</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="12"/>
+        <v>5.7459677419354843E-2</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="13"/>
+        <v>0.40649496080627101</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="14"/>
+        <v>0.89401477853899125</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="16"/>
+        <v>2.2593612109242343</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="17"/>
+        <v>1.897547601151087</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="18"/>
+        <v>1.897547601151087</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>238493</v>
       </c>
@@ -1220,8 +1689,76 @@
       <c r="M8">
         <v>93.620999999999995</v>
       </c>
+      <c r="P8">
+        <f t="shared" si="15"/>
+        <v>0.45582257549548005</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="4"/>
+        <v>0.83870967741935487</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="5"/>
+        <v>0.62857142857142867</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="6"/>
+        <v>0.55400605183528484</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="8"/>
+        <v>0.57835820895522383</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="9"/>
+        <v>5.1679586563307183E-3</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="10"/>
+        <v>3.2806933588557456E-2</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="11"/>
+        <v>6.2790697674418604E-5</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="12"/>
+        <v>9.2741935483870969E-2</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="13"/>
+        <v>0.12334026555751078</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="14"/>
+        <v>0.21339446195524756</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="16"/>
+        <v>1.7372924906905118</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="17"/>
+        <v>2.4438127223209465</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="18"/>
+        <v>1.7372924906905118</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>230098</v>
       </c>
@@ -1258,8 +1795,76 @@
       <c r="M9">
         <v>172.07499999999999</v>
       </c>
+      <c r="P9">
+        <f t="shared" si="15"/>
+        <v>0.41581723827359934</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="4"/>
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="5"/>
+        <v>0.67755102040816317</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="6"/>
+        <v>0.79871069596105781</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="7"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="8"/>
+        <v>0.74152884227511084</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="9"/>
+        <v>9.5607235142118871E-2</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="10"/>
+        <v>0.15776040835858987</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="11"/>
+        <v>3.0066445182724255E-5</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="12"/>
+        <v>6.2644009216589858E-2</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="14"/>
+        <v>0.89461390849809408</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="16"/>
+        <v>2.0420521714569624</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="17"/>
+        <v>2.2091349441053221</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="18"/>
+        <v>2.0420521714569624</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>214666</v>
       </c>
@@ -1296,8 +1901,76 @@
       <c r="M10">
         <v>109.024</v>
       </c>
+      <c r="P10">
+        <f t="shared" si="15"/>
+        <v>0.34227794536019102</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="4"/>
+        <v>0.67741935483870963</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="5"/>
+        <v>0.66938775510204074</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="6"/>
+        <v>0.17116168925141428</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="7"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="8"/>
+        <v>0.51089148850342869</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="9"/>
+        <v>7.8811369509043896E-2</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="10"/>
+        <v>0.76817142553304618</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="11"/>
+        <v>6.6279069767441869E-4</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="12"/>
+        <v>8.9861751152073732E-2</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="13"/>
+        <v>0.48328267477203651</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="14"/>
+        <v>0.34713937152135599</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="16"/>
+        <v>1.5320769480116152</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="17"/>
+        <v>2.3502489222829164</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="18"/>
+        <v>1.5320769480116152</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>209906</v>
       </c>
@@ -1334,8 +2007,88 @@
       <c r="M11">
         <v>132.06200000000001</v>
       </c>
+      <c r="P11">
+        <f t="shared" si="15"/>
+        <v>0.31959475236720086</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="4"/>
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="5"/>
+        <v>0.65918367346938789</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="6"/>
+        <v>0.63557426654387594</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="8"/>
+        <v>0.83844292053247271</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="9"/>
+        <v>8.9147286821705432E-2</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="10"/>
+        <v>0.21412240123358325</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="11"/>
+        <v>1.5747508305647844E-4</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="12"/>
+        <v>0.18058755760368664</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="13"/>
+        <v>0.52487601983682608</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="14"/>
+        <v>0.54717931351862958</v>
+      </c>
+      <c r="AC11">
+        <f>SQRT(
+($P$1 - P11)^2 +
+($Q$1 -Q11)^2 +
+($R$1 - R11)^2 +
+($S$1 - S11)^2 +
+($T$1 - T11)^2 +
+($U$1 - U11)^2 +
+($V$1 - V11)^2 +
+($W$1 - W11)^2 +
+($X$1 - X11)^2 +
+($Y$1 - Y11)^2 +
+($Z$1 - Z11)^2 +
+($AA$1 - AA11)^2)</f>
+        <v>1.9084185791599186</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="17"/>
+        <v>2.1125907830626516</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="18"/>
+        <v>1.9084185791599186</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>279373</v>
       </c>
@@ -1372,8 +2125,76 @@
       <c r="M12">
         <v>75.367000000000004</v>
       </c>
+      <c r="P12">
+        <f t="shared" si="15"/>
+        <v>0.65063117414116001</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="4"/>
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="6"/>
+        <v>0.65662412840415729</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="7"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="8"/>
+        <v>0.85830980233965293</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="9"/>
+        <v>0.19121447028423769</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="10"/>
+        <v>0.34598819588451113</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="11"/>
+        <v>2.4916943521594683E-3</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="12"/>
+        <v>0.23243087557603684</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="13"/>
+        <v>0.20332746760518317</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="14"/>
+        <v>5.489419712243962E-2</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="16"/>
+        <v>1.6087062896423061</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="17"/>
+        <v>2.4004362769312833</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="18"/>
+        <v>1.6087062896423061</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>206267</v>
       </c>
@@ -1410,8 +2231,76 @@
       <c r="M13">
         <v>91.626000000000005</v>
       </c>
+      <c r="P13">
+        <f t="shared" si="15"/>
+        <v>0.30225354663159348</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="4"/>
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="5"/>
+        <v>0.75510204081632648</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="6"/>
+        <v>0.32508880410472307</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="7"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="8"/>
+        <v>0.39905203711173848</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="9"/>
+        <v>4.9095607235142093E-2</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="10"/>
+        <v>0.8925931833891636</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="12"/>
+        <v>0.13594470046082952</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="13"/>
+        <v>0.50247960326347785</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="14"/>
+        <v>0.19607179139857778</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="16"/>
+        <v>1.7884631592625184</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="17"/>
+        <v>2.2591515448180228</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="18"/>
+        <v>1.7884631592625184</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>152946</v>
       </c>
@@ -1448,8 +2337,76 @@
       <c r="M14">
         <v>100.105</v>
       </c>
+      <c r="P14">
+        <f t="shared" si="15"/>
+        <v>4.8158896719991233E-2</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="4"/>
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="5"/>
+        <v>0.82040816326530619</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="6"/>
+        <v>0.49085646625444018</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="8"/>
+        <v>0.44090359015732145</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="9"/>
+        <v>5.2971576227390176E-2</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="10"/>
+        <v>0.6448131015047589</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="11"/>
+        <v>0.95847176079734231</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="12"/>
+        <v>9.7062211981566823E-2</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="13"/>
+        <v>0.38569828827387626</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="14"/>
+        <v>0.26969531202514613</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="16"/>
+        <v>1.8772806642114623</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="17"/>
+        <v>2.1519829562580086</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="18"/>
+        <v>1.8772806642114623</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>212480</v>
       </c>
@@ -1486,8 +2443,76 @@
       <c r="M15">
         <v>95.597999999999999</v>
       </c>
+      <c r="P15">
+        <f t="shared" si="15"/>
+        <v>0.33186083193946064</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="4"/>
+        <v>0.54838709677419351</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="5"/>
+        <v>0.64897959183673481</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="6"/>
+        <v>0.51453756084725699</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="7"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="8"/>
+        <v>0.744655102864058</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="9"/>
+        <v>0.37726098191214474</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="10"/>
+        <v>0.81708938161322919</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="11"/>
+        <v>4.3189368770764125E-5</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="12"/>
+        <v>8.8421658986175114E-2</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="13"/>
+        <v>0.39369700847864342</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="14"/>
+        <v>0.2305608377399776</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="16"/>
+        <v>1.7905739878400384</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="17"/>
+        <v>2.0882105417468408</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="18"/>
+        <v>1.7905739878400384</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>241146</v>
       </c>
@@ -1524,8 +2549,76 @@
       <c r="M16">
         <v>85.471000000000004</v>
       </c>
+      <c r="P16">
+        <f t="shared" si="15"/>
+        <v>0.46846511982539663</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="4"/>
+        <v>0.45161290322580644</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="5"/>
+        <v>0.69591836734693868</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="6"/>
+        <v>0.5934745428233128</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="7"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="8"/>
+        <v>0.73003227107704716</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="9"/>
+        <v>7.2351421188630458E-2</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="10"/>
+        <v>0.57675333652363492</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="11"/>
+        <v>5.4651162790697672E-5</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="12"/>
+        <v>8.4101382488479245E-2</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="13"/>
+        <v>0.19212925931850905</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="14"/>
+        <v>0.14262766243802483</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="16"/>
+        <v>1.6124647194851403</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="17"/>
+        <v>2.304836949551937</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="18"/>
+        <v>1.6124647194851403</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>185228</v>
       </c>
@@ -1562,8 +2655,76 @@
       <c r="M17">
         <v>121.69499999999999</v>
       </c>
+      <c r="P17">
+        <f t="shared" si="15"/>
+        <v>0.20199478667791296</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="4"/>
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="5"/>
+        <v>0.37346938775510202</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="6"/>
+        <v>0.25009867122747009</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="7"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="8"/>
+        <v>0.46389673255344893</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="9"/>
+        <v>0.12919896640826872</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="10"/>
+        <v>0.66395491040569998</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="11"/>
+        <v>3.0398671096345517E-4</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="12"/>
+        <v>0.1028225806451613</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="13"/>
+        <v>8.3346664533674605E-2</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="14"/>
+        <v>0.45716220792414491</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="16"/>
+        <v>1.3125901805240408</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="17"/>
+        <v>2.4817248522303617</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="18"/>
+        <v>1.3125901805240408</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>259558</v>
       </c>
@@ -1600,8 +2761,76 @@
       <c r="M18">
         <v>139.05600000000001</v>
       </c>
+      <c r="P18">
+        <f t="shared" si="15"/>
+        <v>0.55620523524281973</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="4"/>
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="5"/>
+        <v>0.24081632653061225</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="6"/>
+        <v>0.16721484015261148</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="8"/>
+        <v>0.22075433642597822</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="9"/>
+        <v>0.14082687338501287</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="10"/>
+        <v>0.82666028606369979</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="11"/>
+        <v>3.4883720930232562E-3</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="12"/>
+        <v>7.3876728110599074E-2</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="13"/>
+        <v>0.16333386658134699</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="14"/>
+        <v>0.60790851546015801</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="16"/>
+        <v>1.3353206550251377</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="17"/>
+        <v>2.6102046962185113</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="18"/>
+        <v>1.3353206550251377</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>185421</v>
       </c>
@@ -1638,8 +2867,76 @@
       <c r="M19">
         <v>76.778999999999996</v>
       </c>
+      <c r="P19">
+        <f t="shared" si="15"/>
+        <v>0.20291450437699848</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="4"/>
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="5"/>
+        <v>0.18571428571428578</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="6"/>
+        <v>0.11722141823444285</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="9"/>
+        <v>0.31395348837209303</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="10"/>
+        <v>0.96809698516509823</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="11"/>
+        <v>0.40697674418604657</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="12"/>
+        <v>7.5892857142857137E-2</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="14"/>
+        <v>6.7154653676834472E-2</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="16"/>
+        <v>1.4561416353579675</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="17"/>
+        <v>2.6521578768495151</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="18"/>
+        <v>1.4561416353579675</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>211674</v>
       </c>
@@ -1676,8 +2973,76 @@
       <c r="M20">
         <v>162.761</v>
       </c>
+      <c r="P20">
+        <f t="shared" si="15"/>
+        <v>0.32801993833602577</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="4"/>
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="5"/>
+        <v>0.38571428571428573</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="6"/>
+        <v>0.23562689119852653</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="7"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="8"/>
+        <v>0.47035094796288823</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="9"/>
+        <v>0.13436692506459944</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="10"/>
+        <v>0.78093263146700698</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="12"/>
+        <v>4.1474654377880192E-2</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="13"/>
+        <v>0.33770596704527278</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="14"/>
+        <v>0.81374004706209246</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="16"/>
+        <v>1.5370108601001315</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="17"/>
+        <v>2.3464763577212238</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="18"/>
+        <v>1.5370108601001315</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>196973</v>
       </c>
@@ -1714,8 +3079,76 @@
       <c r="M21">
         <v>98.039000000000001</v>
       </c>
+      <c r="P21">
+        <f t="shared" si="15"/>
+        <v>0.25796413577511235</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="4"/>
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="5"/>
+        <v>0.6673469387755101</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="6"/>
+        <v>0.5053282462833838</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="7"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="8"/>
+        <v>0.6678096006454215</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="9"/>
+        <v>0.38113695090439281</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="10"/>
+        <v>0.85324613175945141</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="11"/>
+        <v>3.7707641196013287E-5</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="12"/>
+        <v>6.8260368663594459E-2</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="13"/>
+        <v>0.47048472244440892</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="14"/>
+        <v>0.25175614542360225</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="16"/>
+        <v>1.7477654621093495</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="17"/>
+        <v>2.1399072902762888</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="18"/>
+        <v>1.7477654621093495</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>352687</v>
       </c>
@@ -1752,8 +3185,76 @@
       <c r="M22">
         <v>156.17500000000001</v>
       </c>
+      <c r="P22">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="4"/>
+        <v>0.64516129032258063</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="5"/>
+        <v>0.30816326530612248</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="6"/>
+        <v>0.44349427706880667</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="8"/>
+        <v>0.39209358612343687</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="9"/>
+        <v>8.3979328165374623E-2</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="10"/>
+        <v>0.91492529377359499</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="11"/>
+        <v>1.4750830564784053E-4</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="12"/>
+        <v>0.10570276497695852</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="13"/>
+        <v>0.24972004479283319</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="14"/>
+        <v>0.75655352661786812</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="16"/>
+        <v>2.0052658144813633</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="17"/>
+        <v>2.1412252519194519</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="18"/>
+        <v>2.0052658144813633</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>213732</v>
       </c>
@@ -1790,8 +3291,76 @@
       <c r="M23">
         <v>98.384</v>
       </c>
+      <c r="P23">
+        <f t="shared" si="15"/>
+        <v>0.33782708354181856</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="4"/>
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="5"/>
+        <v>0.82244897959183683</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="6"/>
+        <v>0.77239836863570588</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="8"/>
+        <v>0.62656313029447352</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="9"/>
+        <v>0.4909560723514213</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="10"/>
+        <v>0.2864359015260276</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="12"/>
+        <v>9.5622119815668205E-2</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="13"/>
+        <v>0.4352903535434331</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="14"/>
+        <v>0.25475179521911662</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="16"/>
+        <v>1.6558935872333771</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="17"/>
+        <v>2.2959942316105058</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="18"/>
+        <v>1.6558935872333771</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>178320</v>
       </c>
@@ -1828,8 +3397,76 @@
       <c r="M24">
         <v>79.168000000000006</v>
       </c>
+      <c r="P24">
+        <f t="shared" si="15"/>
+        <v>0.16907556457800207</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="4"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="5"/>
+        <v>0.63061224489795931</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="6"/>
+        <v>0.35534798052887778</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="7"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="8"/>
+        <v>0.40913674868898753</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="9"/>
+        <v>0.2868217054263566</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="10"/>
+        <v>0.50975700537034085</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="11"/>
+        <v>1E-3</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="12"/>
+        <v>7.7620967741935484E-2</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="13"/>
+        <v>0.39529675251959684</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="14"/>
+        <v>8.7898443130410675E-2</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="16"/>
+        <v>1.1616363618348051</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="17"/>
+        <v>2.5612463150671747</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" si="18"/>
+        <v>1.1616363618348051</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>201493</v>
       </c>
@@ -1866,8 +3503,76 @@
       <c r="M25">
         <v>87.085999999999999</v>
       </c>
+      <c r="P25">
+        <f t="shared" si="15"/>
+        <v>0.27950363836509456</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="4"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="6"/>
+        <v>0.77371398500197353</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="7"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="9"/>
+        <v>0.30361757105943149</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="10"/>
+        <v>0.51082043919817099</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="13"/>
+        <v>0.16813309870420731</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="14"/>
+        <v>0.15665077669818611</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="16"/>
+        <v>1.9983539355053765</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="17"/>
+        <v>2.282479453143786</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="18"/>
+        <v>1.9983539355053765</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>224893</v>
       </c>
@@ -1904,8 +3609,76 @@
       <c r="M26">
         <v>87.347999999999999</v>
       </c>
+      <c r="P26">
+        <f t="shared" si="15"/>
+        <v>0.3910134526583654</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="4"/>
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="5"/>
+        <v>0.42448979591836739</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="8"/>
+        <v>1.4118596208148324E-2</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="9"/>
+        <v>0.26873385012919893</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="10"/>
+        <v>0.89152974956133357</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="11"/>
+        <v>2.7242524916943523E-3</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="12"/>
+        <v>8.8421658986175114E-2</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="13"/>
+        <v>8.6546152615581504E-2</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="14"/>
+        <v>0.1589257339341999</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="16"/>
+        <v>1.531325350053653</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="17"/>
+        <v>2.6545789783670464</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="18"/>
+        <v>1.531325350053653</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>221813</v>
       </c>
@@ -1942,8 +3715,76 @@
       <c r="M27">
         <v>107.428</v>
       </c>
+      <c r="P27">
+        <f t="shared" si="15"/>
+        <v>0.37633609248643057</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="4"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="5"/>
+        <v>0.74693877551020404</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="6"/>
+        <v>0.71056439942112881</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="7"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="8"/>
+        <v>0.5843081887858006</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="9"/>
+        <v>0.12919896640826872</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="10"/>
+        <v>8.0236082309778287E-2</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="12"/>
+        <v>6.3508064516129031E-2</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="13"/>
+        <v>0.20492721164613661</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="14"/>
+        <v>0.33328123507602003</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="16"/>
+        <v>1.4202105495195843</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="17"/>
+        <v>2.4634658313574587</v>
+      </c>
+      <c r="AE27">
+        <f t="shared" si="18"/>
+        <v>1.4202105495195843</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG27">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>207600</v>
       </c>
@@ -1980,8 +3821,76 @@
       <c r="M28">
         <v>179.44300000000001</v>
       </c>
+      <c r="P28">
+        <f t="shared" si="15"/>
+        <v>0.30860579374496655</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="4"/>
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="5"/>
+        <v>0.25714285714285717</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="6"/>
+        <v>0.61057755558479154</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="7"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="8"/>
+        <v>0.69776119402985071</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="9"/>
+        <v>0.16795865633074938</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="10"/>
+        <v>0.63630563088211833</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="11"/>
+        <v>5.4651162790697672E-3</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="12"/>
+        <v>8.1221198156682037E-2</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="13"/>
+        <v>0.40649496080627101</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="14"/>
+        <v>0.95859056847881796</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="16"/>
+        <v>1.7033340397061014</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="17"/>
+        <v>2.2266152183238019</v>
+      </c>
+      <c r="AE28">
+        <f t="shared" si="18"/>
+        <v>1.7033340397061014</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>142840</v>
       </c>
@@ -2018,8 +3927,76 @@
       <c r="M29">
         <v>93.296999999999997</v>
       </c>
+      <c r="P29">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="4"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="5"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="6"/>
+        <v>0.82896987238521247</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="8"/>
+        <v>0.88221056877773285</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="9"/>
+        <v>0.37596899224806202</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="10"/>
+        <v>0.29813367363215826</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="12"/>
+        <v>0.17338709677419356</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="13"/>
+        <v>0.56167013277875544</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="14"/>
+        <v>0.21058115606032976</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="16"/>
+        <v>1.9183573797932514</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="17"/>
+        <v>2.2380874561626469</v>
+      </c>
+      <c r="AE29">
+        <f t="shared" si="18"/>
+        <v>1.9183573797932514</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>270426</v>
       </c>
@@ -2056,8 +4033,76 @@
       <c r="M30">
         <v>139.785</v>
       </c>
+      <c r="P30">
+        <f t="shared" si="15"/>
+        <v>0.60799534899236107</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="4"/>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="5"/>
+        <v>0.65714285714285725</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="6"/>
+        <v>0.41981318247599009</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="7"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="8"/>
+        <v>0.64431222267043153</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="9"/>
+        <v>5.4263565891472854E-2</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="10"/>
+        <v>0.72244377093635359</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="12"/>
+        <v>5.9475806451612906E-2</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="13"/>
+        <v>0.13293872980323149</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="14"/>
+        <v>0.61423845372372299</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="16"/>
+        <v>1.6043207421232728</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="17"/>
+        <v>2.3211836108145745</v>
+      </c>
+      <c r="AE30">
+        <f t="shared" si="18"/>
+        <v>1.6043207421232728</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>303593</v>
       </c>
@@ -2094,8 +4139,76 @@
       <c r="M31">
         <v>95.257999999999996</v>
       </c>
+      <c r="P31">
+        <f t="shared" si="15"/>
+        <v>0.76604859731137442</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="4"/>
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="5"/>
+        <v>0.42448979591836739</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="6"/>
+        <v>0.85528219971056441</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="7"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="8"/>
+        <v>0.86183945139169005</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="9"/>
+        <v>3.2299741602067167E-2</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="10"/>
+        <v>5.6361992874993348E-3</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="11"/>
+        <v>2.9900332225913621E-5</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="12"/>
+        <v>3.7010368663594473E-2</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="13"/>
+        <v>0.46088625819868828</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="14"/>
+        <v>0.22760860315889098</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="16"/>
+        <v>1.633074373714976</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="17"/>
+        <v>2.5002711644826512</v>
+      </c>
+      <c r="AE31">
+        <f t="shared" si="18"/>
+        <v>1.633074373714976</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG31">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>230108</v>
       </c>
@@ -2132,8 +4245,76 @@
       <c r="M32">
         <v>91.647999999999996</v>
       </c>
+      <c r="P32">
+        <f t="shared" si="15"/>
+        <v>0.41586489204039134</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="4"/>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="5"/>
+        <v>0.62448979591836751</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="6"/>
+        <v>0.66451782660176295</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="8"/>
+        <v>0.72650262202501004</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="9"/>
+        <v>0.42764857881136958</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="10"/>
+        <v>0.40554049024299471</v>
+      </c>
+      <c r="X32">
+        <f t="shared" si="11"/>
+        <v>5.3820598006644525E-4</v>
+      </c>
+      <c r="Y32">
+        <f t="shared" si="12"/>
+        <v>0.363479262672811</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="13"/>
+        <v>0.23532234842425215</v>
+      </c>
+      <c r="AA32">
+        <f t="shared" si="14"/>
+        <v>0.19626281834205977</v>
+      </c>
+      <c r="AC32">
+        <f t="shared" si="16"/>
+        <v>1.6810980692060249</v>
+      </c>
+      <c r="AD32">
+        <f t="shared" si="17"/>
+        <v>2.1489021607743366</v>
+      </c>
+      <c r="AE32">
+        <f t="shared" si="18"/>
+        <v>1.6810980692060249</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG32">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>193373</v>
       </c>
@@ -2170,8 +4351,76 @@
       <c r="M33">
         <v>119.22</v>
       </c>
+      <c r="P33">
+        <f t="shared" si="15"/>
+        <v>0.24080877972999376</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="4"/>
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="5"/>
+        <v>0.42448979591836739</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="6"/>
+        <v>0.63031180107880558</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="7"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="8"/>
+        <v>0.83743444937474765</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="9"/>
+        <v>0.1731266149870801</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="10"/>
+        <v>0.29813367363215826</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="11"/>
+        <v>2.4750830564784055E-5</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="12"/>
+        <v>8.2661290322580627E-2</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="13"/>
+        <v>0.2305231163013918</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="14"/>
+        <v>0.43567167678241164</v>
+      </c>
+      <c r="AC33">
+        <f t="shared" si="16"/>
+        <v>1.5168826295836715</v>
+      </c>
+      <c r="AD33">
+        <f t="shared" si="17"/>
+        <v>2.3714734928337173</v>
+      </c>
+      <c r="AE33">
+        <f t="shared" si="18"/>
+        <v>1.5168826295836715</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG33">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>222293</v>
       </c>
@@ -2208,8 +4457,76 @@
       <c r="M34">
         <v>135.25700000000001</v>
       </c>
+      <c r="P34">
+        <f t="shared" si="15"/>
+        <v>0.37862347329244639</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="4"/>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="5"/>
+        <v>0.62653061224489803</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="6"/>
+        <v>0.32640442047099066</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="7"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="8"/>
+        <v>0.72357805566760791</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="9"/>
+        <v>0.14470284237726097</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="10"/>
+        <v>0.83304088903068019</v>
+      </c>
+      <c r="X34">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <f t="shared" si="12"/>
+        <v>6.3652073732718903E-2</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="13"/>
+        <v>0.23852183650615905</v>
+      </c>
+      <c r="AA34">
+        <f t="shared" si="14"/>
+        <v>0.57492163553795805</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="16"/>
+        <v>1.7299672272986877</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="17"/>
+        <v>2.2549630573950932</v>
+      </c>
+      <c r="AE34">
+        <f t="shared" si="18"/>
+        <v>1.7299672272986877</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>220720</v>
       </c>
@@ -2246,8 +4563,76 @@
       <c r="M35">
         <v>141.36000000000001</v>
       </c>
+      <c r="P35">
+        <f t="shared" si="15"/>
+        <v>0.37112753577606544</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="4"/>
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="5"/>
+        <v>0.45102040816326538</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="6"/>
+        <v>0.37771345875542695</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="7"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="8"/>
+        <v>0.66659943525615162</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="9"/>
+        <v>0.20284237726098195</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="10"/>
+        <v>0.84048492582549061</v>
+      </c>
+      <c r="X35">
+        <f t="shared" si="11"/>
+        <v>5.0996677740863794E-4</v>
+      </c>
+      <c r="Y35">
+        <f t="shared" si="12"/>
+        <v>6.2644009216589858E-2</v>
+      </c>
+      <c r="Z35">
+        <f t="shared" si="13"/>
+        <v>0.26091825307950733</v>
+      </c>
+      <c r="AA35">
+        <f t="shared" si="14"/>
+        <v>0.62791424626846248</v>
+      </c>
+      <c r="AC35">
+        <f t="shared" si="16"/>
+        <v>1.4874593297814147</v>
+      </c>
+      <c r="AD35">
+        <f t="shared" si="17"/>
+        <v>2.3954650669891144</v>
+      </c>
+      <c r="AE35">
+        <f t="shared" si="18"/>
+        <v>1.4874593297814147</v>
+      </c>
+      <c r="AF35">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG35">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>231693</v>
       </c>
@@ -2284,8 +4669,76 @@
       <c r="M36">
         <v>167.64699999999999</v>
       </c>
+      <c r="P36">
+        <f t="shared" si="15"/>
+        <v>0.4234180140769227</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="4"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="5"/>
+        <v>0.37959183673469388</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="6"/>
+        <v>0.52111564267859489</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="8"/>
+        <v>0.81070996369503823</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="9"/>
+        <v>0.1459948320413437</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="10"/>
+        <v>0.48210772584675926</v>
+      </c>
+      <c r="X36">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="12"/>
+        <v>0.14314516129032256</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="13"/>
+        <v>0.3025115981442969</v>
+      </c>
+      <c r="AA36">
+        <f t="shared" si="14"/>
+        <v>0.85616539460088392</v>
+      </c>
+      <c r="AC36">
+        <f t="shared" si="16"/>
+        <v>1.8376519912720193</v>
+      </c>
+      <c r="AD36">
+        <f t="shared" si="17"/>
+        <v>2.2192034286308715</v>
+      </c>
+      <c r="AE36">
+        <f t="shared" si="18"/>
+        <v>1.8376519912720193</v>
+      </c>
+      <c r="AF36">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG36">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>174933</v>
       </c>
@@ -2322,8 +4775,76 @@
       <c r="M37">
         <v>139.38999999999999</v>
       </c>
+      <c r="P37">
+        <f t="shared" si="15"/>
+        <v>0.15293523376555299</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" ref="Q37:Q55" si="21">(C37 - $C$1)/($C$2 - $C$1)</f>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R37">
+        <f t="shared" ref="R37:R55" si="22">(D37 - $D$1)/($D$2 - $D$1)</f>
+        <v>0.7</v>
+      </c>
+      <c r="S37">
+        <f t="shared" ref="S37:S55" si="23">(E37 - $E$1)/($E$2- $E$1)</f>
+        <v>0.71319563215366399</v>
+      </c>
+      <c r="T37">
+        <f t="shared" ref="T37:T55" si="24">(F37 - $F$1)/($F$2- $F$1)</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U37">
+        <f t="shared" ref="U37:U55" si="25">(G37 - $G$1)/($G$2- $G$1)</f>
+        <v>0.81222267043162544</v>
+      </c>
+      <c r="V37">
+        <f t="shared" ref="V37:V55" si="26">(H37 - $H$1)/($H$2- $H$1)</f>
+        <v>0.12532299741602063</v>
+      </c>
+      <c r="W37">
+        <f t="shared" ref="W37:W55" si="27">(I37 - $I$1)/($I$2- $I$1)</f>
+        <v>0.28537246769819752</v>
+      </c>
+      <c r="X37">
+        <f t="shared" ref="X37:X55" si="28">(J37 - $J$1)/($J$2- $J$1)</f>
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" ref="Y37:Y55" si="29">(K37 - $K$1)/($K$2- $K$1)</f>
+        <v>7.4740783410138248E-2</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" ref="Z37:Z55" si="30">(L37 - $L$1)/($L$2- $L$1)</f>
+        <v>0.81762917933130697</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" ref="AA37:AA55" si="31">(M37 - $M$1)/($M$2- $M$1)</f>
+        <v>0.61080865178393107</v>
+      </c>
+      <c r="AC37">
+        <f t="shared" si="16"/>
+        <v>1.7654959078366099</v>
+      </c>
+      <c r="AD37">
+        <f t="shared" si="17"/>
+        <v>2.2456145034768791</v>
+      </c>
+      <c r="AE37">
+        <f t="shared" si="18"/>
+        <v>1.7654959078366099</v>
+      </c>
+      <c r="AF37">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG37">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>291533</v>
       </c>
@@ -2360,8 +4881,76 @@
       <c r="M38">
         <v>152.65100000000001</v>
       </c>
+      <c r="P38">
+        <f t="shared" si="15"/>
+        <v>0.70857815456022721</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="21"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="22"/>
+        <v>0.3693877551020408</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="23"/>
+        <v>0.73029864491514285</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="24"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="25"/>
+        <v>0.68646631706333194</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="26"/>
+        <v>0.29198966408268734</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="27"/>
+        <v>1.6642739405540494E-2</v>
+      </c>
+      <c r="X38">
+        <f t="shared" si="28"/>
+        <v>3.3554817275747512E-4</v>
+      </c>
+      <c r="Y38">
+        <f t="shared" si="29"/>
+        <v>9.8502304147465441E-2</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="30"/>
+        <v>0.35370340745480727</v>
+      </c>
+      <c r="AA38">
+        <f t="shared" si="31"/>
+        <v>0.72595448348919411</v>
+      </c>
+      <c r="AC38">
+        <f t="shared" si="16"/>
+        <v>1.7731793175442365</v>
+      </c>
+      <c r="AD38">
+        <f t="shared" si="17"/>
+        <v>2.2278774781675712</v>
+      </c>
+      <c r="AE38">
+        <f t="shared" si="18"/>
+        <v>1.7731793175442365</v>
+      </c>
+      <c r="AF38">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG38">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>287346</v>
       </c>
@@ -2398,8 +4987,76 @@
       <c r="M39">
         <v>128.96899999999999</v>
       </c>
+      <c r="P39">
+        <f t="shared" si="15"/>
+        <v>0.68862552240441843</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="21"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="22"/>
+        <v>0.6183673469387756</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="23"/>
+        <v>0.14221812919352717</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="24"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="25"/>
+        <v>0.22509076240419515</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="26"/>
+        <v>0.12532299741602063</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="27"/>
+        <v>0.88408571276652315</v>
+      </c>
+      <c r="X39">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <f t="shared" si="29"/>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="30"/>
+        <v>0.40969444888817791</v>
+      </c>
+      <c r="AA39">
+        <f t="shared" si="31"/>
+        <v>0.52032266187362697</v>
+      </c>
+      <c r="AC39">
+        <f t="shared" si="16"/>
+        <v>1.5516054520428109</v>
+      </c>
+      <c r="AD39">
+        <f t="shared" si="17"/>
+        <v>2.3945912065529122</v>
+      </c>
+      <c r="AE39">
+        <f t="shared" si="18"/>
+        <v>1.5516054520428109</v>
+      </c>
+      <c r="AF39">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG39">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>182186</v>
       </c>
@@ -2436,8 +5093,76 @@
       <c r="M40">
         <v>145.77199999999999</v>
       </c>
+      <c r="P40">
+        <f t="shared" si="15"/>
+        <v>0.18749851081978774</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="21"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="22"/>
+        <v>0.65510204081632673</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="23"/>
+        <v>0.13958689646099198</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="24"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="25"/>
+        <v>0.18293666801129488</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="26"/>
+        <v>0.23643410852713179</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="27"/>
+        <v>0.96916041899292826</v>
+      </c>
+      <c r="X40">
+        <f t="shared" si="28"/>
+        <v>3.6877076411960134E-4</v>
+      </c>
+      <c r="Y40">
+        <f t="shared" si="29"/>
+        <v>0.15178571428571427</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="30"/>
+        <v>0.50887857942729164</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" si="31"/>
+        <v>0.6662238314795037</v>
+      </c>
+      <c r="AC40">
+        <f t="shared" si="16"/>
+        <v>1.6712954664878252</v>
+      </c>
+      <c r="AD40">
+        <f t="shared" si="17"/>
+        <v>2.3706858411493141</v>
+      </c>
+      <c r="AE40">
+        <f t="shared" si="18"/>
+        <v>1.6712954664878252</v>
+      </c>
+      <c r="AF40">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>169920</v>
       </c>
@@ -2474,8 +5199,76 @@
       <c r="M41">
         <v>171.92</v>
       </c>
+      <c r="P41">
+        <f t="shared" si="15"/>
+        <v>0.12904640047272536</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="21"/>
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="22"/>
+        <v>0.34081632653061233</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="23"/>
+        <v>0.68030522299697405</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="24"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="25"/>
+        <v>0.73023396530859208</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="26"/>
+        <v>8.3979328165374623E-2</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="27"/>
+        <v>0.26942096028074658</v>
+      </c>
+      <c r="X41">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <f t="shared" si="29"/>
+        <v>0.37788018433179715</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="30"/>
+        <v>0.79043353063509836</v>
+      </c>
+      <c r="AA41">
+        <f t="shared" si="31"/>
+        <v>0.893268036850834</v>
+      </c>
+      <c r="AC41">
+        <f t="shared" si="16"/>
+        <v>1.6865737395499323</v>
+      </c>
+      <c r="AD41">
+        <f t="shared" si="17"/>
+        <v>2.3458537742075958</v>
+      </c>
+      <c r="AE41">
+        <f t="shared" si="18"/>
+        <v>1.6865737395499323</v>
+      </c>
+      <c r="AF41">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>156146</v>
       </c>
@@ -2512,8 +5305,76 @@
       <c r="M42">
         <v>114.142</v>
       </c>
+      <c r="P42">
+        <f t="shared" si="15"/>
+        <v>6.340810209342998E-2</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="21"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="22"/>
+        <v>0.84489795918367361</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="23"/>
+        <v>0.14353374555979476</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="24"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="25"/>
+        <v>0.29729729729729731</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="26"/>
+        <v>0.17571059431524547</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="27"/>
+        <v>0.93619397033019625</v>
+      </c>
+      <c r="X42">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <f t="shared" si="29"/>
+        <v>9.994239631336406E-2</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="30"/>
+        <v>0.24652055671092629</v>
+      </c>
+      <c r="AA42">
+        <f t="shared" si="31"/>
+        <v>0.39157918500959477</v>
+      </c>
+      <c r="AC42">
+        <f t="shared" si="16"/>
+        <v>1.6239076293652632</v>
+      </c>
+      <c r="AD42">
+        <f t="shared" si="17"/>
+        <v>2.531599563837704</v>
+      </c>
+      <c r="AE42">
+        <f t="shared" si="18"/>
+        <v>1.6239076293652632</v>
+      </c>
+      <c r="AF42">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>286093</v>
       </c>
@@ -2550,8 +5411,76 @@
       <c r="M43">
         <v>69.045000000000002</v>
       </c>
+      <c r="P43">
+        <f t="shared" si="15"/>
+        <v>0.68265450542538131</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="21"/>
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="22"/>
+        <v>0.3836734693877551</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="23"/>
+        <v>0.23694250756479412</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="24"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="25"/>
+        <v>4.0641387656312894E-2</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="26"/>
+        <v>0.24289405684754525</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="27"/>
+        <v>0.99361939703301971</v>
+      </c>
+      <c r="X43">
+        <f t="shared" si="28"/>
+        <v>3.4717607973421925E-5</v>
+      </c>
+      <c r="Y43">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="30"/>
+        <v>0.6192609182530795</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <f t="shared" si="16"/>
+        <v>1.95132251563279</v>
+      </c>
+      <c r="AD43">
+        <f t="shared" si="17"/>
+        <v>2.3205079680765097</v>
+      </c>
+      <c r="AE43">
+        <f t="shared" si="18"/>
+        <v>1.95132251563279</v>
+      </c>
+      <c r="AF43">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>206268</v>
       </c>
@@ -2588,8 +5517,76 @@
       <c r="M44">
         <v>118.68600000000001</v>
       </c>
+      <c r="P44">
+        <f t="shared" si="15"/>
+        <v>0.30225831200827269</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="21"/>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="22"/>
+        <v>0.92040816326530628</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="23"/>
+        <v>0.94605972898302859</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="24"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="25"/>
+        <v>0.85114965711980628</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="26"/>
+        <v>0.49224806201550403</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="27"/>
+        <v>0.14606263625245922</v>
+      </c>
+      <c r="X44">
+        <f t="shared" si="28"/>
+        <v>3.4883720930232559E-4</v>
+      </c>
+      <c r="Y44">
+        <f t="shared" si="29"/>
+        <v>6.5092165898617521E-2</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="30"/>
+        <v>0.92801151815709493</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="31"/>
+        <v>0.43103493188152864</v>
+      </c>
+      <c r="AC44">
+        <f t="shared" si="16"/>
+        <v>1.9909549374766757</v>
+      </c>
+      <c r="AD44">
+        <f t="shared" si="17"/>
+        <v>2.2349573767518107</v>
+      </c>
+      <c r="AE44">
+        <f t="shared" si="18"/>
+        <v>1.9909549374766757</v>
+      </c>
+      <c r="AF44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG44">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>151333</v>
       </c>
@@ -2626,8 +5623,76 @@
       <c r="M45">
         <v>80.338999999999999</v>
       </c>
+      <c r="P45">
+        <f t="shared" si="15"/>
+        <v>4.0472344136442268E-2</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="21"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="22"/>
+        <v>0.65102040816326545</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="23"/>
+        <v>0.38297592422049731</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="24"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="25"/>
+        <v>0.41962484872932626</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="26"/>
+        <v>6.2015503875968978E-2</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="27"/>
+        <v>0.90322752166746423</v>
+      </c>
+      <c r="X45">
+        <f t="shared" si="28"/>
+        <v>3.4219269102990033E-3</v>
+      </c>
+      <c r="Y45">
+        <f t="shared" si="29"/>
+        <v>0.12154377880184332</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" si="30"/>
+        <v>0.69284914413693821</v>
+      </c>
+      <c r="AA45">
+        <f t="shared" si="31"/>
+        <v>9.8066286349388257E-2</v>
+      </c>
+      <c r="AC45">
+        <f t="shared" si="16"/>
+        <v>1.7028844440607467</v>
+      </c>
+      <c r="AD45">
+        <f t="shared" si="17"/>
+        <v>2.5033341983497004</v>
+      </c>
+      <c r="AE45">
+        <f t="shared" si="18"/>
+        <v>1.7028844440607467</v>
+      </c>
+      <c r="AF45">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG45">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>209051</v>
       </c>
@@ -2664,8 +5729,76 @@
       <c r="M46">
         <v>172.709</v>
       </c>
+      <c r="P46">
+        <f t="shared" si="15"/>
+        <v>0.3155203553064852</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="21"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="22"/>
+        <v>0.36530612244897959</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="23"/>
+        <v>0.68425207209577688</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="24"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="25"/>
+        <v>0.81655909640984259</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="26"/>
+        <v>8.0103359173126623E-2</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="27"/>
+        <v>0.23113734247886425</v>
+      </c>
+      <c r="X46">
+        <f t="shared" si="28"/>
+        <v>1.8438538205980066E-5</v>
+      </c>
+      <c r="Y46">
+        <f t="shared" si="29"/>
+        <v>0.40812211981566815</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" si="30"/>
+        <v>0.72484402495600719</v>
+      </c>
+      <c r="AA46">
+        <f t="shared" si="31"/>
+        <v>0.90011895768753214</v>
+      </c>
+      <c r="AC46">
+        <f t="shared" si="16"/>
+        <v>1.7288902266977622</v>
+      </c>
+      <c r="AD46">
+        <f t="shared" si="17"/>
+        <v>2.2914800084993994</v>
+      </c>
+      <c r="AE46">
+        <f t="shared" si="18"/>
+        <v>1.7288902266977622</v>
+      </c>
+      <c r="AF46">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG46">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>211600</v>
       </c>
@@ -2702,8 +5835,76 @@
       <c r="M47">
         <v>97.814999999999998</v>
       </c>
+      <c r="P47">
+        <f t="shared" si="15"/>
+        <v>0.32766730046176501</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="21"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="22"/>
+        <v>0.67551020408163254</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="23"/>
+        <v>0.77108275226943834</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="25"/>
+        <v>0.96036708350141176</v>
+      </c>
+      <c r="V47">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="27"/>
+        <v>7.4174509491146928E-2</v>
+      </c>
+      <c r="X47">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <f t="shared" si="29"/>
+        <v>0.19066820276497695</v>
+      </c>
+      <c r="Z47">
+        <f t="shared" si="30"/>
+        <v>0.79683250679891215</v>
+      </c>
+      <c r="AA47">
+        <f t="shared" si="31"/>
+        <v>0.24981114381723932</v>
+      </c>
+      <c r="AC47">
+        <f t="shared" si="16"/>
+        <v>1.9554845039801849</v>
+      </c>
+      <c r="AD47">
+        <f t="shared" si="17"/>
+        <v>2.3669938700531246</v>
+      </c>
+      <c r="AE47">
+        <f t="shared" si="18"/>
+        <v>1.9554845039801849</v>
+      </c>
+      <c r="AF47">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG47">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>309746</v>
       </c>
@@ -2740,8 +5941,76 @@
       <c r="M48">
         <v>184.21199999999999</v>
       </c>
+      <c r="P48">
+        <f t="shared" si="15"/>
+        <v>0.7953699600184897</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="21"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="22"/>
+        <v>0.17142857142857146</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="23"/>
+        <v>0.47243783712669385</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="25"/>
+        <v>0.64895118999596602</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="26"/>
+        <v>0.81912144702842382</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="27"/>
+        <v>0.7458393151486149</v>
+      </c>
+      <c r="X48">
+        <f t="shared" si="28"/>
+        <v>2.0930232558139536E-4</v>
+      </c>
+      <c r="Y48">
+        <f t="shared" si="29"/>
+        <v>8.1221198156682037E-2</v>
+      </c>
+      <c r="Z48">
+        <f t="shared" si="30"/>
+        <v>0.58406654935210378</v>
+      </c>
+      <c r="AA48">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="AC48">
+        <f t="shared" si="16"/>
+        <v>1.9766936392417995</v>
+      </c>
+      <c r="AD48">
+        <f t="shared" si="17"/>
+        <v>2.2242855835291127</v>
+      </c>
+      <c r="AE48">
+        <f t="shared" si="18"/>
+        <v>1.9766936392417995</v>
+      </c>
+      <c r="AF48">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG48">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>200040</v>
       </c>
@@ -2778,8 +6047,76 @@
       <c r="M49">
         <v>176.49</v>
       </c>
+      <c r="P49">
+        <f t="shared" si="15"/>
+        <v>0.27257954605021756</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="21"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="22"/>
+        <v>0.49591836734693878</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="23"/>
+        <v>0.55663728456782002</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="24"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="25"/>
+        <v>0.88987494957644209</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="26"/>
+        <v>0.33979328165374678</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="27"/>
+        <v>0.23539107779018453</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <f t="shared" si="29"/>
+        <v>5.0835253456221197E-2</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="30"/>
+        <v>0.76483762597984317</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="31"/>
+        <v>0.93294954283779219</v>
+      </c>
+      <c r="AC49">
+        <f t="shared" si="16"/>
+        <v>1.8323938262545001</v>
+      </c>
+      <c r="AD49">
+        <f t="shared" si="17"/>
+        <v>2.2350784769155934</v>
+      </c>
+      <c r="AE49">
+        <f t="shared" si="18"/>
+        <v>1.8323938262545001</v>
+      </c>
+      <c r="AF49">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG49">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>345026</v>
       </c>
@@ -2816,8 +6153,76 @@
       <c r="M50">
         <v>86.582999999999998</v>
       </c>
+      <c r="P50">
+        <f t="shared" si="15"/>
+        <v>0.96349244926065181</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="21"/>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="22"/>
+        <v>0.31020408163265312</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="23"/>
+        <v>0.65267727930535457</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="24"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="25"/>
+        <v>0.67728922952803539</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="26"/>
+        <v>4.7803617571059415E-2</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="27"/>
+        <v>0.28111873238687729</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="28"/>
+        <v>3.7375415282392029E-2</v>
+      </c>
+      <c r="Y50">
+        <f t="shared" si="29"/>
+        <v>7.3444700460829501E-2</v>
+      </c>
+      <c r="Z50">
+        <f t="shared" si="30"/>
+        <v>0.18892977123660215</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="31"/>
+        <v>0.15228320612675506</v>
+      </c>
+      <c r="AC50">
+        <f t="shared" si="16"/>
+        <v>1.5098020081593098</v>
+      </c>
+      <c r="AD50">
+        <f t="shared" si="17"/>
+        <v>2.5185530991105831</v>
+      </c>
+      <c r="AE50">
+        <f t="shared" si="18"/>
+        <v>1.5098020081593098</v>
+      </c>
+      <c r="AF50">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG50">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>159173</v>
       </c>
@@ -2854,8 +6259,76 @@
       <c r="M51">
         <v>139.797</v>
       </c>
+      <c r="P51">
+        <f t="shared" si="15"/>
+        <v>7.7832897301367193E-2</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="22"/>
+        <v>0.68571428571428561</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="23"/>
+        <v>0.14748059465859756</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="25"/>
+        <v>0.34721661960467926</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="26"/>
+        <v>0.16020671834625322</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="27"/>
+        <v>0.99787313234433983</v>
+      </c>
+      <c r="X51">
+        <f t="shared" si="28"/>
+        <v>1.0382059800664453E-3</v>
+      </c>
+      <c r="Y51">
+        <f t="shared" si="29"/>
+        <v>0.25403225806451613</v>
+      </c>
+      <c r="Z51">
+        <f t="shared" si="30"/>
+        <v>0.61446168613021912</v>
+      </c>
+      <c r="AA51">
+        <f t="shared" si="31"/>
+        <v>0.61434265023834955</v>
+      </c>
+      <c r="AC51">
+        <f t="shared" si="16"/>
+        <v>1.8599737769002005</v>
+      </c>
+      <c r="AD51">
+        <f t="shared" si="17"/>
+        <v>2.3788872091780746</v>
+      </c>
+      <c r="AE51">
+        <f t="shared" si="18"/>
+        <v>1.8599737769002005</v>
+      </c>
+      <c r="AF51">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>346397</v>
       </c>
@@ -2892,8 +6365,76 @@
       <c r="M52">
         <v>88.054000000000002</v>
       </c>
+      <c r="P52">
+        <f t="shared" si="15"/>
+        <v>0.97002578068783452</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="21"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="22"/>
+        <v>0.10612244897959182</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="23"/>
+        <v>0.133008814629654</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="24"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="25"/>
+        <v>0.30264219443323914</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="26"/>
+        <v>0.18992248062015507</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="27"/>
+        <v>0.9606529483702877</v>
+      </c>
+      <c r="X52">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <f t="shared" si="29"/>
+        <v>0.16474654377880185</v>
+      </c>
+      <c r="Z52">
+        <f t="shared" si="30"/>
+        <v>0.16333386658134699</v>
+      </c>
+      <c r="AA52">
+        <f t="shared" si="31"/>
+        <v>0.16505596221139737</v>
+      </c>
+      <c r="AC52">
+        <f t="shared" si="16"/>
+        <v>1.5913693348872802</v>
+      </c>
+      <c r="AD52">
+        <f t="shared" si="17"/>
+        <v>2.574126329756643</v>
+      </c>
+      <c r="AE52">
+        <f t="shared" si="18"/>
+        <v>1.5913693348872802</v>
+      </c>
+      <c r="AF52">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG52">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>247133</v>
       </c>
@@ -2930,8 +6471,76 @@
       <c r="M53">
         <v>148.654</v>
       </c>
+      <c r="P53">
+        <f t="shared" si="15"/>
+        <v>0.49699543000376467</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="21"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="22"/>
+        <v>0.34693877551020419</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="23"/>
+        <v>0.344823049598737</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="24"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="25"/>
+        <v>0.62938684953610324</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="26"/>
+        <v>0.12015503875968991</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="27"/>
+        <v>0.72244377093635359</v>
+      </c>
+      <c r="X53">
+        <f t="shared" si="28"/>
+        <v>9.4352159468438553E-3</v>
+      </c>
+      <c r="Y53">
+        <f t="shared" si="29"/>
+        <v>4.9395161290322578E-2</v>
+      </c>
+      <c r="Z53">
+        <f t="shared" si="30"/>
+        <v>0.29771236602143658</v>
+      </c>
+      <c r="AA53">
+        <f t="shared" si="31"/>
+        <v>0.69124836107565535</v>
+      </c>
+      <c r="AC53">
+        <f t="shared" si="16"/>
+        <v>1.5481830680597051</v>
+      </c>
+      <c r="AD53">
+        <f t="shared" si="17"/>
+        <v>2.3617881454687568</v>
+      </c>
+      <c r="AE53">
+        <f t="shared" si="18"/>
+        <v>1.5481830680597051</v>
+      </c>
+      <c r="AF53">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG53">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>206636</v>
       </c>
@@ -2968,8 +6577,76 @@
       <c r="M54">
         <v>107.98099999999999</v>
       </c>
+      <c r="P54">
+        <f t="shared" si="15"/>
+        <v>0.30401197062621815</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="21"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="22"/>
+        <v>0.91428571428571448</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="23"/>
+        <v>0.60136824102091835</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="24"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="25"/>
+        <v>0.64068172650262201</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="26"/>
+        <v>0.18863049095607234</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <f t="shared" si="29"/>
+        <v>8.8421658986175114E-2</v>
+      </c>
+      <c r="Z54">
+        <f t="shared" si="30"/>
+        <v>0.49448088305871057</v>
+      </c>
+      <c r="AA54">
+        <f t="shared" si="31"/>
+        <v>0.33808295779172853</v>
+      </c>
+      <c r="AC54">
+        <f t="shared" si="16"/>
+        <v>1.8202866984964519</v>
+      </c>
+      <c r="AD54">
+        <f t="shared" si="17"/>
+        <v>2.2661405982664373</v>
+      </c>
+      <c r="AE54">
+        <f t="shared" si="18"/>
+        <v>1.8202866984964519</v>
+      </c>
+      <c r="AF54">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG54">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>276146</v>
       </c>
@@ -3005,6 +6682,97 @@
       </c>
       <c r="M55">
         <v>139.31</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="15"/>
+        <v>0.63525330359738286</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="22"/>
+        <v>0.46326530612244904</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="23"/>
+        <v>0.22247072753585054</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="24"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="25"/>
+        <v>0.37736990722065339</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="26"/>
+        <v>0.24806201550387597</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="27"/>
+        <v>0.92449619822406559</v>
+      </c>
+      <c r="X55">
+        <f t="shared" si="28"/>
+        <v>4.7009966777408643E-4</v>
+      </c>
+      <c r="Y55">
+        <f t="shared" si="29"/>
+        <v>8.4101382488479245E-2</v>
+      </c>
+      <c r="Z55">
+        <f t="shared" si="30"/>
+        <v>0.12973924172132459</v>
+      </c>
+      <c r="AA55">
+        <f t="shared" si="31"/>
+        <v>0.61011400835308738</v>
+      </c>
+      <c r="AC55">
+        <f t="shared" si="16"/>
+        <v>1.7172308166620376</v>
+      </c>
+      <c r="AD55">
+        <f t="shared" si="17"/>
+        <v>2.3958329404701959</v>
+      </c>
+      <c r="AE55">
+        <f t="shared" si="18"/>
+        <v>1.7172308166620376</v>
+      </c>
+      <c r="AF55">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AG55">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AE56">
+        <f>SUM(AE5:AE55)</f>
+        <v>86.929696532993802</v>
+      </c>
+      <c r="AF56">
+        <f>SUM(AF5:AF55)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="P58" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="Q59" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
+++ b/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Práctica 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal del laboratorio\1924910\Tareas\Minería de datos\Práctica 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3590779-F7A7-4F3E-9859-2D94FC2A9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B0EAA5F-3816-4796-860C-BD0B64EC5768}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="ca_cest_brandi_carlile - copia" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>MIN:</t>
   </si>
@@ -77,25 +76,10 @@
     <t>Tempo</t>
   </si>
   <si>
-    <t>Duda:</t>
-  </si>
-  <si>
-    <t>¿Es normal que los datos de Loudness los estemos trabajando como positivos?</t>
-  </si>
-  <si>
-    <t>¿Cuántas veces repito esto?</t>
-  </si>
-  <si>
     <t>DC0</t>
   </si>
   <si>
     <t>DC1</t>
-  </si>
-  <si>
-    <t>Distancia aeuclidian: Resta de las coordenadas de ambos puntos en la misma dimensión al cuadrado, sumada a tra´ves de todas las dimensiones en raíz</t>
-  </si>
-  <si>
-    <t>dcmin</t>
   </si>
   <si>
     <t>c0</t>
@@ -103,12 +87,22 @@
   <si>
     <t>c1</t>
   </si>
+  <si>
+    <t>Distancia a grupo más cercano</t>
+  </si>
+  <si>
+    <t>Suma solo los Cluster0, Los suma a "0" (Min de Duración) ¿Por qué?
+Luego los divide entre "Total de Cluster0 + 1". ¿Qué?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0.000000000"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +237,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,8 +424,32 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB3B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -540,6 +564,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -585,9 +689,30 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -633,8 +758,48 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB3B3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB3B3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFB3B3"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -962,416 +1127,451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9653E2FD-8EE4-4C35-A4F1-EC87F3E3C160}">
-  <dimension ref="A1:AG59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="11.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
+    <row r="1" spans="1:33">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14">
         <f>MIN(B5:B55)</f>
         <v>142840</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="14">
         <f t="shared" ref="C1:M1" si="0">MIN(C5:C55)</f>
         <v>40</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="14">
         <f t="shared" si="0"/>
         <v>0.23599999999999999</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="14">
         <f t="shared" si="0"/>
         <v>7.8899999999999998E-2</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="14">
         <f t="shared" si="0"/>
         <v>-13.988</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="14">
         <f t="shared" si="0"/>
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="14">
         <f t="shared" si="0"/>
         <v>1.65E-3</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="14">
         <f t="shared" si="0"/>
         <v>4.4600000000000001E-2</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="14">
         <f t="shared" si="0"/>
         <v>9.9900000000000003E-2</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="14">
         <f t="shared" si="0"/>
         <v>69.045000000000002</v>
       </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1">
+      <c r="O1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="14">
         <f>MIN(P5:P55)</f>
         <v>0</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="14">
         <f t="shared" ref="Q1:AA1" si="1">MIN(Q5:Q55)</f>
         <v>0</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W1">
+      <c r="W1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X1">
+      <c r="X1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y1">
+      <c r="Y1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z1">
+      <c r="Z1" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA1">
+      <c r="AA1" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF1">
+    </row>
+    <row r="2" spans="1:33">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16">
+        <f>MAX(B5:B55)</f>
+        <v>352687</v>
+      </c>
+      <c r="C2" s="16">
+        <f t="shared" ref="C2:M2" si="2">MAX(C5:C55)</f>
+        <v>71</v>
+      </c>
+      <c r="D2" s="16">
+        <f t="shared" si="2"/>
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="E2" s="16">
+        <f t="shared" si="2"/>
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="F2" s="16">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="G2" s="16">
+        <f t="shared" si="2"/>
+        <v>-4.0720000000000001</v>
+      </c>
+      <c r="H2" s="16">
+        <f t="shared" si="2"/>
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I2" s="16">
+        <f t="shared" si="2"/>
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="J2" s="16">
+        <f t="shared" si="2"/>
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="K2" s="16">
+        <f t="shared" si="2"/>
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="L2" s="16">
+        <f>MAX(L5:L55)</f>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M2" s="17">
+        <f t="shared" si="2"/>
+        <v>184.21199999999999</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="16">
+        <f>MAX(P5:P55)</f>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="16">
+        <f t="shared" ref="Q2:AA2" si="3">MAX(Q5:Q55)</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="U2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="W2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="X2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Y2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Z2" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AA2" s="17">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1"/>
+      <c r="AF2">
         <f>(SUMPRODUCT(P5:P55,AF5:AF55)+P1)/(AF56+1)</f>
         <v>0.39292103294304903</v>
       </c>
+      <c r="AG2" s="22" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <f>MAX(B5:B55)</f>
-        <v>352687</v>
-      </c>
-      <c r="C2">
-        <f t="shared" ref="C2:M2" si="2">MAX(C5:C55)</f>
-        <v>71</v>
-      </c>
-      <c r="D2">
-        <f t="shared" si="2"/>
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="E2">
-        <f t="shared" si="2"/>
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="F2">
-        <f t="shared" si="2"/>
+    <row r="3" spans="1:33">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="6"/>
+    </row>
+    <row r="4" spans="1:33">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
-        <f t="shared" si="2"/>
-        <v>-4.0720000000000001</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="2"/>
-        <v>0.10299999999999999</v>
-      </c>
-      <c r="I2">
-        <f t="shared" si="2"/>
+      <c r="L4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="4"/>
+      <c r="P4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC4" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5">
+        <v>265306</v>
+      </c>
+      <c r="C5" s="5">
+        <v>60</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>-12.382</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="I5" s="5">
         <v>0.94199999999999995</v>
       </c>
-      <c r="J2">
-        <f t="shared" si="2"/>
-        <v>6.0199999999999997E-2</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="2"/>
-        <v>0.73899999999999999</v>
-      </c>
-      <c r="L2">
-        <f>MAX(L5:L55)</f>
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="M2">
-        <f t="shared" si="2"/>
-        <v>184.21199999999999</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <f>MAX(P5:P55)</f>
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" ref="Q2:AA2" si="3">MAX(Q5:Q55)</f>
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" t="s">
-        <v>5</v>
-      </c>
-      <c r="T4" t="s">
-        <v>6</v>
-      </c>
-      <c r="U4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V4" t="s">
-        <v>8</v>
-      </c>
-      <c r="W4" t="s">
-        <v>9</v>
-      </c>
-      <c r="X4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>265306</v>
-      </c>
-      <c r="C5">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>0.45200000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.32900000000000001</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>-12.382</v>
-      </c>
-      <c r="H5">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="I5">
-        <v>0.94199999999999995</v>
-      </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>1.2800000000000001E-3</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>9.7900000000000001E-2</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>0.19800000000000001</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="6">
         <v>82.766999999999996</v>
       </c>
-      <c r="P5">
+      <c r="O5" s="4"/>
+      <c r="P5" s="10">
         <f>(B5 - $B$1)/($B$2 - $B$1)</f>
         <v>0.58359662039485916</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="10">
         <f t="shared" ref="Q5:Q36" si="4">(C5 - $C$1)/($C$2 - $C$1)</f>
         <v>0.64516129032258063</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="10">
         <f t="shared" ref="R5:R36" si="5">(D5 - $D$1)/($D$2 - $D$1)</f>
         <v>0.44081632653061231</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="10">
         <f t="shared" ref="S5:S36" si="6">(E5 - $E$1)/($E$2- $E$1)</f>
         <v>0.32903565320352585</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="10">
         <f t="shared" ref="T5:T36" si="7">(F5 - $F$1)/($F$2- $F$1)</f>
         <v>0.72727272727272729</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="10">
         <f t="shared" ref="U5:U36" si="8">(G5 - $G$1)/($G$2- $G$1)</f>
         <v>0.16196046793061716</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="10">
         <f t="shared" ref="V5:V36" si="9">(H5 - $H$1)/($H$2- $H$1)</f>
         <v>0.2183462532299742</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="10">
         <f t="shared" ref="W5:W36" si="10">(I5 - $I$1)/($I$2- $I$1)</f>
         <v>1</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="10">
         <f t="shared" ref="X5:X36" si="11">(J5 - $J$1)/($J$2- $J$1)</f>
         <v>2.1262458471760802E-2</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="10">
         <f t="shared" ref="Y5:Y36" si="12">(K5 - $K$1)/($K$2- $K$1)</f>
         <v>7.6756912442396311E-2</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="10">
         <f t="shared" ref="Z5:Z36" si="13">(L5 - $L$1)/($L$2- $L$1)</f>
         <v>0.1569348904175332</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="11">
         <f t="shared" ref="AA5:AA36" si="14">(M5 - $M$1)/($M$2- $M$1)</f>
         <v>0.11914871447550075</v>
       </c>
-      <c r="AC5">
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="18">
         <f>SQRT(
 ($P$1 - P5)^2 +
 ($Q$1 -Q5)^2 +
@@ -1387,7 +1587,7 @@
 ($AA$1 - AA5)^2)</f>
         <v>1.645418546063</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="19">
         <f>SQRT(
 ($P$2 - P5)^2 +
 ($Q$2 -Q5)^2 +
@@ -1403,7 +1603,7 @@
 ($AA$2 - AA5)^2)</f>
         <v>2.3972520856897592</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="2">
         <f>MIN(AC5:AD5)</f>
         <v>1.645418546063</v>
       </c>
@@ -1416,92 +1616,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B6">
+    <row r="6" spans="1:33">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5">
         <v>268653</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="5">
         <v>71</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>0.29699999999999999</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <v>0.83899999999999997</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="5">
         <v>-4.4480000000000004</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>8.48E-2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>0.39900000000000002</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
         <v>9.6500000000000002E-2</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>0.30299999999999999</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="6">
         <v>152.99700000000001</v>
       </c>
-      <c r="P6">
+      <c r="O6" s="4"/>
+      <c r="P6" s="10">
         <f t="shared" ref="P6:P55" si="15">(B6 - $B$1)/($B$2 - $B$1)</f>
         <v>0.59954633614014019</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="10">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="10">
         <f t="shared" si="5"/>
         <v>0.12448979591836734</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="10">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="10">
         <f t="shared" si="7"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="10">
         <f t="shared" si="8"/>
         <v>0.962081484469544</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="10">
         <f t="shared" si="9"/>
         <v>0.76485788113695097</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="10">
         <f t="shared" si="10"/>
         <v>0.42255543148827573</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="10">
         <f t="shared" si="12"/>
         <v>7.4740783410138248E-2</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="10">
         <f t="shared" si="13"/>
         <v>0.32490801471764519</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="11">
         <f t="shared" si="14"/>
         <v>0.72895881632759407</v>
       </c>
-      <c r="AC6">
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="18">
         <f t="shared" ref="AC6:AC55" si="16">SQRT(
 ($P$1 - P6)^2 +
 ($Q$1 -Q6)^2 +
@@ -1517,7 +1720,7 @@
 ($AA$1 - AA6)^2)</f>
         <v>2.2608861113651288</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="19">
         <f t="shared" ref="AD6:AD55" si="17">SQRT(
 ($P$2 - P6)^2 +
 ($Q$2 -Q6)^2 +
@@ -1533,7 +1736,7 @@
 ($AA$2 - AA6)^2)</f>
         <v>1.9582138924589287</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="2">
         <f t="shared" ref="AE6:AE55" si="18">MIN(AC6:AD6)</f>
         <v>1.9582138924589287</v>
       </c>
@@ -1546,100 +1749,103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B7">
+    <row r="7" spans="1:33">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5">
         <v>231000</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="5">
         <v>68</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="5">
         <v>0.503</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <v>0.72199999999999998</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>-7.5949999999999998</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>3.5200000000000002E-5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>0.35399999999999998</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="6">
         <v>172.006</v>
       </c>
-      <c r="P7">
+      <c r="O7" s="4"/>
+      <c r="P7" s="10">
         <f t="shared" si="15"/>
         <v>0.42011560803823739</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="10">
         <f t="shared" si="4"/>
         <v>0.90322580645161288</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="10">
         <f t="shared" si="5"/>
         <v>0.54489795918367356</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="10">
         <f t="shared" si="6"/>
         <v>0.84607288514669121</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="10">
         <f t="shared" si="8"/>
         <v>0.64471561113352149</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="10">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="10">
         <f t="shared" si="10"/>
         <v>0.21624926888924337</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="10">
         <f t="shared" si="11"/>
         <v>5.8471760797342194E-4</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="10">
         <f t="shared" si="12"/>
         <v>5.7459677419354843E-2</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="10">
         <f t="shared" si="13"/>
         <v>0.40649496080627101</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="11">
         <f t="shared" si="14"/>
         <v>0.89401477853899125</v>
       </c>
-      <c r="AC7">
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="18">
         <f t="shared" si="16"/>
         <v>2.2593612109242343</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="19">
         <f t="shared" si="17"/>
         <v>1.897547601151087</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="2">
         <f t="shared" si="18"/>
         <v>1.897547601151087</v>
       </c>
@@ -1652,100 +1858,103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B8">
+    <row r="8" spans="1:33">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5">
         <v>238493</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="5">
         <v>66</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="5">
         <v>0.54400000000000004</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <v>0.5</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="5">
         <v>-8.2530000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>3.7799999999999998E-6</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>0.109</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>0.17699999999999999</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="6">
         <v>93.620999999999995</v>
       </c>
-      <c r="P8">
+      <c r="O8" s="4"/>
+      <c r="P8" s="10">
         <f t="shared" si="15"/>
         <v>0.45582257549548005</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="10">
         <f t="shared" si="4"/>
         <v>0.83870967741935487</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="10">
         <f t="shared" si="5"/>
         <v>0.62857142857142867</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="10">
         <f t="shared" si="6"/>
         <v>0.55400605183528484</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="10">
         <f t="shared" si="8"/>
         <v>0.57835820895522383</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="10">
         <f t="shared" si="9"/>
         <v>5.1679586563307183E-3</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="10">
         <f t="shared" si="10"/>
         <v>3.2806933588557456E-2</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="10">
         <f t="shared" si="11"/>
         <v>6.2790697674418604E-5</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="10">
         <f t="shared" si="12"/>
         <v>9.2741935483870969E-2</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="10">
         <f t="shared" si="13"/>
         <v>0.12334026555751078</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="11">
         <f t="shared" si="14"/>
         <v>0.21339446195524756</v>
       </c>
-      <c r="AC8">
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="18">
         <f t="shared" si="16"/>
         <v>1.7372924906905118</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="19">
         <f t="shared" si="17"/>
         <v>2.4438127223209465</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="2">
         <f t="shared" si="18"/>
         <v>1.7372924906905118</v>
       </c>
@@ -1758,100 +1967,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B9">
+    <row r="9" spans="1:33">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5">
         <v>230098</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>62</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="5">
         <v>0.56799999999999995</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="5">
         <v>0.68600000000000005</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
         <v>-6.6349999999999998</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>0.15</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>1.81E-6</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>8.8099999999999998E-2</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>0.72499999999999998</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="6">
         <v>172.07499999999999</v>
       </c>
-      <c r="P9">
+      <c r="O9" s="4"/>
+      <c r="P9" s="10">
         <f t="shared" si="15"/>
         <v>0.41581723827359934</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="10">
         <f t="shared" si="4"/>
         <v>0.70967741935483875</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="10">
         <f t="shared" si="5"/>
         <v>0.67755102040816317</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="10">
         <f t="shared" si="6"/>
         <v>0.79871069596105781</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="10">
         <f t="shared" si="7"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="10">
         <f t="shared" si="8"/>
         <v>0.74152884227511084</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="10">
         <f t="shared" si="9"/>
         <v>9.5607235142118871E-2</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="10">
         <f t="shared" si="10"/>
         <v>0.15776040835858987</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="10">
         <f t="shared" si="11"/>
         <v>3.0066445182724255E-5</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="10">
         <f t="shared" si="12"/>
         <v>6.2644009216589858E-2</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="10">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="11">
         <f t="shared" si="14"/>
         <v>0.89461390849809408</v>
       </c>
-      <c r="AC9">
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="18">
         <f t="shared" si="16"/>
         <v>2.0420521714569624</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="19">
         <f t="shared" si="17"/>
         <v>2.2091349441053221</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="2">
         <f t="shared" si="18"/>
         <v>2.0420521714569624</v>
       </c>
@@ -1864,100 +2076,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B10">
+    <row r="10" spans="1:33">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5">
         <v>214666</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5">
         <v>61</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="5">
         <v>0.56399999999999995</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="5">
         <v>0.20899999999999999</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="5">
         <v>3</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="5">
         <v>-8.9220000000000006</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="5">
         <v>0.72399999999999998</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="5">
         <v>3.9900000000000001E-5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="5">
         <v>0.107</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="5">
         <v>0.40200000000000002</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="6">
         <v>109.024</v>
       </c>
-      <c r="P10">
+      <c r="O10" s="4"/>
+      <c r="P10" s="10">
         <f t="shared" si="15"/>
         <v>0.34227794536019102</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="10">
         <f t="shared" si="4"/>
         <v>0.67741935483870963</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="10">
         <f t="shared" si="5"/>
         <v>0.66938775510204074</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="10">
         <f t="shared" si="6"/>
         <v>0.17116168925141428</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="10">
         <f t="shared" si="7"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="10">
         <f t="shared" si="8"/>
         <v>0.51089148850342869</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="10">
         <f t="shared" si="9"/>
         <v>7.8811369509043896E-2</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="10">
         <f t="shared" si="10"/>
         <v>0.76817142553304618</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="10">
         <f t="shared" si="11"/>
         <v>6.6279069767441869E-4</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="10">
         <f t="shared" si="12"/>
         <v>8.9861751152073732E-2</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="10">
         <f t="shared" si="13"/>
         <v>0.48328267477203651</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="11">
         <f t="shared" si="14"/>
         <v>0.34713937152135599</v>
       </c>
-      <c r="AC10">
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="18">
         <f t="shared" si="16"/>
         <v>1.5320769480116152</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="19">
         <f t="shared" si="17"/>
         <v>2.3502489222829164</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="2">
         <f t="shared" si="18"/>
         <v>1.5320769480116152</v>
       </c>
@@ -1970,92 +2185,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B11">
+    <row r="11" spans="1:33">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5">
         <v>209906</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="5">
         <v>58</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="5">
         <v>0.55900000000000005</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="5">
         <v>0.56200000000000006</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="5">
         <v>11</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="5">
         <v>-5.6740000000000004</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>0.20300000000000001</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="5">
         <v>9.4800000000000007E-6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
         <v>0.17</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="5">
         <v>0.42799999999999999</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="6">
         <v>132.06200000000001</v>
       </c>
-      <c r="P11">
+      <c r="O11" s="4"/>
+      <c r="P11" s="10">
         <f t="shared" si="15"/>
         <v>0.31959475236720086</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="10">
         <f t="shared" si="4"/>
         <v>0.58064516129032262</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="10">
         <f t="shared" si="5"/>
         <v>0.65918367346938789</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="10">
         <f t="shared" si="6"/>
         <v>0.63557426654387594</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="10">
         <f t="shared" si="8"/>
         <v>0.83844292053247271</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="10">
         <f t="shared" si="9"/>
         <v>8.9147286821705432E-2</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="10">
         <f t="shared" si="10"/>
         <v>0.21412240123358325</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="10">
         <f t="shared" si="11"/>
         <v>1.5747508305647844E-4</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="10">
         <f t="shared" si="12"/>
         <v>0.18058755760368664</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="10">
         <f t="shared" si="13"/>
         <v>0.52487601983682608</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="11">
         <f t="shared" si="14"/>
         <v>0.54717931351862958</v>
       </c>
-      <c r="AC11">
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="18">
         <f>SQRT(
 ($P$1 - P11)^2 +
 ($Q$1 -Q11)^2 +
@@ -2071,11 +2289,11 @@
 ($AA$1 - AA11)^2)</f>
         <v>1.9084185791599186</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="19">
         <f t="shared" si="17"/>
         <v>2.1125907830626516</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="2">
         <f t="shared" si="18"/>
         <v>1.9084185791599186</v>
       </c>
@@ -2088,100 +2306,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B12">
+    <row r="12" spans="1:33">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5">
         <v>279373</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="5">
         <v>58</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="5">
         <v>0.23599999999999999</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>0.57799999999999996</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="5">
         <v>7</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="5">
         <v>-5.4770000000000003</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="5">
         <v>0.32700000000000001</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="5">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="5">
         <v>0.20599999999999999</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="5">
         <v>0.22700000000000001</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="6">
         <v>75.367000000000004</v>
       </c>
-      <c r="P12">
+      <c r="O12" s="4"/>
+      <c r="P12" s="10">
         <f t="shared" si="15"/>
         <v>0.65063117414116001</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="10">
         <f t="shared" si="4"/>
         <v>0.58064516129032262</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="10">
         <f t="shared" si="6"/>
         <v>0.65662412840415729</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="10">
         <f t="shared" si="7"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="10">
         <f t="shared" si="8"/>
         <v>0.85830980233965293</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="10">
         <f t="shared" si="9"/>
         <v>0.19121447028423769</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="10">
         <f t="shared" si="10"/>
         <v>0.34598819588451113</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="10">
         <f t="shared" si="11"/>
         <v>2.4916943521594683E-3</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="10">
         <f t="shared" si="12"/>
         <v>0.23243087557603684</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="10">
         <f t="shared" si="13"/>
         <v>0.20332746760518317</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="11">
         <f t="shared" si="14"/>
         <v>5.489419712243962E-2</v>
       </c>
-      <c r="AC12">
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="18">
         <f t="shared" si="16"/>
         <v>1.6087062896423061</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="19">
         <f t="shared" si="17"/>
         <v>2.4004362769312833</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="2">
         <f t="shared" si="18"/>
         <v>1.6087062896423061</v>
       </c>
@@ -2194,100 +2415,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B13">
+    <row r="13" spans="1:33">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5">
         <v>206267</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="5">
         <v>58</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="5">
         <v>0.60599999999999998</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <v>0.32600000000000001</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="5">
         <v>10</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="5">
         <v>-10.031000000000001</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="5">
         <v>0.84099999999999997</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
         <v>0.13900000000000001</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="5">
         <v>0.41399999999999998</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="6">
         <v>91.626000000000005</v>
       </c>
-      <c r="P13">
+      <c r="O13" s="4"/>
+      <c r="P13" s="10">
         <f t="shared" si="15"/>
         <v>0.30225354663159348</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="10">
         <f t="shared" si="4"/>
         <v>0.58064516129032262</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="10">
         <f t="shared" si="5"/>
         <v>0.75510204081632648</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="10">
         <f t="shared" si="6"/>
         <v>0.32508880410472307</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="10">
         <f t="shared" si="7"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="10">
         <f t="shared" si="8"/>
         <v>0.39905203711173848</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="10">
         <f t="shared" si="9"/>
         <v>4.9095607235142093E-2</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="10">
         <f t="shared" si="10"/>
         <v>0.8925931833891636</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="10">
         <f t="shared" si="12"/>
         <v>0.13594470046082952</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="10">
         <f t="shared" si="13"/>
         <v>0.50247960326347785</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="11">
         <f t="shared" si="14"/>
         <v>0.19607179139857778</v>
       </c>
-      <c r="AC13">
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="18">
         <f t="shared" si="16"/>
         <v>1.7884631592625184</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="19">
         <f t="shared" si="17"/>
         <v>2.2591515448180228</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="2">
         <f t="shared" si="18"/>
         <v>1.7884631592625184</v>
       </c>
@@ -2300,100 +2524,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B14">
+    <row r="14" spans="1:33">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5">
         <v>152946</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="5">
         <v>53</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="5">
         <v>0.63800000000000001</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="5">
         <v>0.45200000000000001</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="5">
         <v>9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="5">
         <v>-9.6159999999999997</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>2.9700000000000001E-2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="5">
         <v>0.60799999999999998</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="5">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="5">
         <v>0.112</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="5">
         <v>0.34100000000000003</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="6">
         <v>100.105</v>
       </c>
-      <c r="P14">
+      <c r="O14" s="4"/>
+      <c r="P14" s="10">
         <f t="shared" si="15"/>
         <v>4.8158896719991233E-2</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="10">
         <f t="shared" si="4"/>
         <v>0.41935483870967744</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="10">
         <f t="shared" si="5"/>
         <v>0.82040816326530619</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="10">
         <f t="shared" si="6"/>
         <v>0.49085646625444018</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="10">
         <f t="shared" si="8"/>
         <v>0.44090359015732145</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="10">
         <f t="shared" si="9"/>
         <v>5.2971576227390176E-2</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="10">
         <f t="shared" si="10"/>
         <v>0.6448131015047589</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="10">
         <f t="shared" si="11"/>
         <v>0.95847176079734231</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="10">
         <f t="shared" si="12"/>
         <v>9.7062211981566823E-2</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="10">
         <f t="shared" si="13"/>
         <v>0.38569828827387626</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="11">
         <f t="shared" si="14"/>
         <v>0.26969531202514613</v>
       </c>
-      <c r="AC14">
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="18">
         <f t="shared" si="16"/>
         <v>1.8772806642114623</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="19">
         <f t="shared" si="17"/>
         <v>2.1519829562580086</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="2">
         <f t="shared" si="18"/>
         <v>1.8772806642114623</v>
       </c>
@@ -2406,100 +2633,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B15">
+    <row r="15" spans="1:33">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5">
         <v>212480</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>57</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="5">
         <v>0.55400000000000005</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="5">
         <v>0.47</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="5">
         <v>8</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="5">
         <v>-6.6040000000000001</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="5">
         <v>0.77</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="5">
         <v>2.6000000000000001E-6</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="5">
         <v>0.106</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="5">
         <v>0.34599999999999997</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="6">
         <v>95.597999999999999</v>
       </c>
-      <c r="P15">
+      <c r="O15" s="4"/>
+      <c r="P15" s="10">
         <f t="shared" si="15"/>
         <v>0.33186083193946064</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="10">
         <f t="shared" si="4"/>
         <v>0.54838709677419351</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="10">
         <f t="shared" si="5"/>
         <v>0.64897959183673481</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="10">
         <f t="shared" si="6"/>
         <v>0.51453756084725699</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="10">
         <f t="shared" si="7"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="10">
         <f t="shared" si="8"/>
         <v>0.744655102864058</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="10">
         <f t="shared" si="9"/>
         <v>0.37726098191214474</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="10">
         <f t="shared" si="10"/>
         <v>0.81708938161322919</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="10">
         <f t="shared" si="11"/>
         <v>4.3189368770764125E-5</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="10">
         <f t="shared" si="12"/>
         <v>8.8421658986175114E-2</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="10">
         <f t="shared" si="13"/>
         <v>0.39369700847864342</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="11">
         <f t="shared" si="14"/>
         <v>0.2305608377399776</v>
       </c>
-      <c r="AC15">
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="18">
         <f t="shared" si="16"/>
         <v>1.7905739878400384</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="19">
         <f t="shared" si="17"/>
         <v>2.0882105417468408</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="2">
         <f t="shared" si="18"/>
         <v>1.7905739878400384</v>
       </c>
@@ -2512,100 +2742,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B16">
+    <row r="16" spans="1:33">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5">
         <v>241146</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="5">
         <v>54</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="5">
         <v>0.57699999999999996</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="5">
         <v>0.53</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="5">
         <v>7</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="5">
         <v>-6.7489999999999997</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="5">
         <v>0.54400000000000004</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="5">
         <v>3.2899999999999998E-6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="5">
         <v>0.10299999999999999</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="5">
         <v>0.22</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="6">
         <v>85.471000000000004</v>
       </c>
-      <c r="P16">
+      <c r="O16" s="4"/>
+      <c r="P16" s="10">
         <f t="shared" si="15"/>
         <v>0.46846511982539663</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="10">
         <f t="shared" si="4"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="10">
         <f t="shared" si="5"/>
         <v>0.69591836734693868</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="10">
         <f t="shared" si="6"/>
         <v>0.5934745428233128</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="10">
         <f t="shared" si="7"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="10">
         <f t="shared" si="8"/>
         <v>0.73003227107704716</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="10">
         <f t="shared" si="9"/>
         <v>7.2351421188630458E-2</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="10">
         <f t="shared" si="10"/>
         <v>0.57675333652363492</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="10">
         <f t="shared" si="11"/>
         <v>5.4651162790697672E-5</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="10">
         <f t="shared" si="12"/>
         <v>8.4101382488479245E-2</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="10">
         <f t="shared" si="13"/>
         <v>0.19212925931850905</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="11">
         <f t="shared" si="14"/>
         <v>0.14262766243802483</v>
       </c>
-      <c r="AC16">
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="18">
         <f t="shared" si="16"/>
         <v>1.6124647194851403</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="19">
         <f t="shared" si="17"/>
         <v>2.304836949551937</v>
       </c>
-      <c r="AE16">
+      <c r="AE16" s="2">
         <f t="shared" si="18"/>
         <v>1.6124647194851403</v>
       </c>
@@ -2618,100 +2851,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B17">
+    <row r="17" spans="1:33">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5">
         <v>185228</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>53</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="5">
         <v>0.41899999999999998</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="5">
         <v>0.26900000000000002</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="5">
         <v>7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="5">
         <v>-9.3879999999999999</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>3.56E-2</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="5">
         <v>0.626</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="5">
         <v>1.8300000000000001E-5</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="5">
         <v>0.11600000000000001</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="5">
         <v>0.152</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="6">
         <v>121.69499999999999</v>
       </c>
-      <c r="P17">
+      <c r="O17" s="4"/>
+      <c r="P17" s="10">
         <f t="shared" si="15"/>
         <v>0.20199478667791296</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="10">
         <f t="shared" si="4"/>
         <v>0.41935483870967744</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="10">
         <f t="shared" si="5"/>
         <v>0.37346938775510202</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="10">
         <f t="shared" si="6"/>
         <v>0.25009867122747009</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="10">
         <f t="shared" si="7"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="10">
         <f t="shared" si="8"/>
         <v>0.46389673255344893</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="10">
         <f t="shared" si="9"/>
         <v>0.12919896640826872</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="10">
         <f t="shared" si="10"/>
         <v>0.66395491040569998</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="10">
         <f t="shared" si="11"/>
         <v>3.0398671096345517E-4</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="10">
         <f t="shared" si="12"/>
         <v>0.1028225806451613</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="10">
         <f t="shared" si="13"/>
         <v>8.3346664533674605E-2</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="11">
         <f t="shared" si="14"/>
         <v>0.45716220792414491</v>
       </c>
-      <c r="AC17">
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="18">
         <f t="shared" si="16"/>
         <v>1.3125901805240408</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="19">
         <f t="shared" si="17"/>
         <v>2.4817248522303617</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="2">
         <f t="shared" si="18"/>
         <v>1.3125901805240408</v>
       </c>
@@ -2724,100 +2960,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B18">
+    <row r="18" spans="1:33">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5">
         <v>259558</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>55</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="5">
         <v>0.35399999999999998</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="5">
         <v>0.20599999999999999</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
         <v>-11.798999999999999</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="5">
         <v>0.77900000000000003</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="5">
         <v>2.1000000000000001E-4</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="5">
         <v>9.5899999999999999E-2</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="5">
         <v>0.20200000000000001</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="6">
         <v>139.05600000000001</v>
       </c>
-      <c r="P18">
+      <c r="O18" s="4"/>
+      <c r="P18" s="10">
         <f t="shared" si="15"/>
         <v>0.55620523524281973</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="10">
         <f t="shared" si="4"/>
         <v>0.4838709677419355</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="10">
         <f t="shared" si="5"/>
         <v>0.24081632653061225</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="10">
         <f t="shared" si="6"/>
         <v>0.16721484015261148</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="10">
         <f t="shared" si="8"/>
         <v>0.22075433642597822</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="10">
         <f t="shared" si="9"/>
         <v>0.14082687338501287</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="10">
         <f t="shared" si="10"/>
         <v>0.82666028606369979</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="10">
         <f t="shared" si="11"/>
         <v>3.4883720930232562E-3</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="10">
         <f t="shared" si="12"/>
         <v>7.3876728110599074E-2</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="10">
         <f t="shared" si="13"/>
         <v>0.16333386658134699</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="11">
         <f t="shared" si="14"/>
         <v>0.60790851546015801</v>
       </c>
-      <c r="AC18">
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="18">
         <f t="shared" si="16"/>
         <v>1.3353206550251377</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="19">
         <f t="shared" si="17"/>
         <v>2.6102046962185113</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="2">
         <f t="shared" si="18"/>
         <v>1.3353206550251377</v>
       </c>
@@ -2830,100 +3069,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B19">
+    <row r="19" spans="1:33">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5">
         <v>185421</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="5">
         <v>52</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="5">
         <v>0.32700000000000001</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="5">
         <v>0.16800000000000001</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="5">
         <v>9</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>-13.988</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>4.99E-2</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="5">
         <v>0.91200000000000003</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="5">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="5">
         <v>9.7299999999999998E-2</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="5">
         <v>9.9900000000000003E-2</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="6">
         <v>76.778999999999996</v>
       </c>
-      <c r="P19">
+      <c r="O19" s="4"/>
+      <c r="P19" s="10">
         <f t="shared" si="15"/>
         <v>0.20291450437699848</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="10">
         <f t="shared" si="4"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="10">
         <f t="shared" si="5"/>
         <v>0.18571428571428578</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="10">
         <f t="shared" si="6"/>
         <v>0.11722141823444285</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="10">
         <f t="shared" si="9"/>
         <v>0.31395348837209303</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="10">
         <f t="shared" si="10"/>
         <v>0.96809698516509823</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="10">
         <f t="shared" si="11"/>
         <v>0.40697674418604657</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="10">
         <f t="shared" si="12"/>
         <v>7.5892857142857137E-2</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="11">
         <f t="shared" si="14"/>
         <v>6.7154653676834472E-2</v>
       </c>
-      <c r="AC19">
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="18">
         <f t="shared" si="16"/>
         <v>1.4561416353579675</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="19">
         <f t="shared" si="17"/>
         <v>2.6521578768495151</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="2">
         <f t="shared" si="18"/>
         <v>1.4561416353579675</v>
       </c>
@@ -2936,100 +3178,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B20">
+    <row r="20" spans="1:33">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5">
         <v>211674</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="5">
         <v>51</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="5">
         <v>0.42499999999999999</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="5">
         <v>0.25800000000000001</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="5">
         <v>6</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="5">
         <v>-9.3239999999999998</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="5">
         <v>0.73599999999999999</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
         <v>7.3400000000000007E-2</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="5">
         <v>0.311</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="6">
         <v>162.761</v>
       </c>
-      <c r="P20">
+      <c r="O20" s="4"/>
+      <c r="P20" s="10">
         <f t="shared" si="15"/>
         <v>0.32801993833602577</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="10">
         <f t="shared" si="4"/>
         <v>0.35483870967741937</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="10">
         <f t="shared" si="5"/>
         <v>0.38571428571428573</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="10">
         <f t="shared" si="6"/>
         <v>0.23562689119852653</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="10">
         <f t="shared" si="7"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="10">
         <f t="shared" si="8"/>
         <v>0.47035094796288823</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="10">
         <f t="shared" si="9"/>
         <v>0.13436692506459944</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="10">
         <f t="shared" si="10"/>
         <v>0.78093263146700698</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="10">
         <f t="shared" si="12"/>
         <v>4.1474654377880192E-2</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="10">
         <f t="shared" si="13"/>
         <v>0.33770596704527278</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="11">
         <f t="shared" si="14"/>
         <v>0.81374004706209246</v>
       </c>
-      <c r="AC20">
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="18">
         <f t="shared" si="16"/>
         <v>1.5370108601001315</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="19">
         <f t="shared" si="17"/>
         <v>2.3464763577212238</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="2">
         <f t="shared" si="18"/>
         <v>1.5370108601001315</v>
       </c>
@@ -3042,100 +3287,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B21">
+    <row r="21" spans="1:33">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5">
         <v>196973</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="5">
         <v>52</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="5">
         <v>0.56299999999999994</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="5">
         <v>0.46300000000000002</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="5">
         <v>8</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="5">
         <v>-7.3659999999999997</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>5.5100000000000003E-2</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="5">
         <v>0.80400000000000005</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="5">
         <v>2.2699999999999999E-6</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="5">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="5">
         <v>0.39400000000000002</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="6">
         <v>98.039000000000001</v>
       </c>
-      <c r="P21">
+      <c r="O21" s="4"/>
+      <c r="P21" s="10">
         <f t="shared" si="15"/>
         <v>0.25796413577511235</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="10">
         <f t="shared" si="4"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="10">
         <f t="shared" si="5"/>
         <v>0.6673469387755101</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="10">
         <f t="shared" si="6"/>
         <v>0.5053282462833838</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="10">
         <f t="shared" si="7"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="10">
         <f t="shared" si="8"/>
         <v>0.6678096006454215</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="10">
         <f t="shared" si="9"/>
         <v>0.38113695090439281</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="10">
         <f t="shared" si="10"/>
         <v>0.85324613175945141</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="10">
         <f t="shared" si="11"/>
         <v>3.7707641196013287E-5</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="10">
         <f t="shared" si="12"/>
         <v>6.8260368663594459E-2</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="10">
         <f t="shared" si="13"/>
         <v>0.47048472244440892</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="11">
         <f t="shared" si="14"/>
         <v>0.25175614542360225</v>
       </c>
-      <c r="AC21">
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="18">
         <f t="shared" si="16"/>
         <v>1.7477654621093495</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="19">
         <f t="shared" si="17"/>
         <v>2.1399072902762888</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="2">
         <f t="shared" si="18"/>
         <v>1.7477654621093495</v>
       </c>
@@ -3148,100 +3396,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B22">
+    <row r="22" spans="1:33">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5">
         <v>352687</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>60</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="5">
         <v>0.38700000000000001</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="5">
         <v>0.41599999999999998</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="5">
         <v>9</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="5">
         <v>-10.1</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="5">
         <v>0.86199999999999999</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="5">
         <v>8.8799999999999997E-6</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="5">
         <v>0.11799999999999999</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="5">
         <v>0.25600000000000001</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="6">
         <v>156.17500000000001</v>
       </c>
-      <c r="P22">
+      <c r="O22" s="4"/>
+      <c r="P22" s="10">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="10">
         <f t="shared" si="4"/>
         <v>0.64516129032258063</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="10">
         <f t="shared" si="5"/>
         <v>0.30816326530612248</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="10">
         <f t="shared" si="6"/>
         <v>0.44349427706880667</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="10">
         <f t="shared" si="8"/>
         <v>0.39209358612343687</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="10">
         <f t="shared" si="9"/>
         <v>8.3979328165374623E-2</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="10">
         <f t="shared" si="10"/>
         <v>0.91492529377359499</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="10">
         <f t="shared" si="11"/>
         <v>1.4750830564784053E-4</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="10">
         <f t="shared" si="12"/>
         <v>0.10570276497695852</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="10">
         <f t="shared" si="13"/>
         <v>0.24972004479283319</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="11">
         <f t="shared" si="14"/>
         <v>0.75655352661786812</v>
       </c>
-      <c r="AC22">
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="18">
         <f t="shared" si="16"/>
         <v>2.0052658144813633</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="19">
         <f t="shared" si="17"/>
         <v>2.1412252519194519</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="2">
         <f t="shared" si="18"/>
         <v>2.0052658144813633</v>
       </c>
@@ -3254,100 +3505,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B23">
+    <row r="23" spans="1:33">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5">
         <v>213732</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>59</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="5">
         <v>0.63900000000000001</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="5">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
         <v>-7.7750000000000004</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="5">
         <v>0.27100000000000002</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
         <v>0.111</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="5">
         <v>0.372</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="6">
         <v>98.384</v>
       </c>
-      <c r="P23">
+      <c r="O23" s="4"/>
+      <c r="P23" s="10">
         <f t="shared" si="15"/>
         <v>0.33782708354181856</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="10">
         <f t="shared" si="4"/>
         <v>0.61290322580645162</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="10">
         <f t="shared" si="5"/>
         <v>0.82244897959183683</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="10">
         <f t="shared" si="6"/>
         <v>0.77239836863570588</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="10">
         <f t="shared" si="8"/>
         <v>0.62656313029447352</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="10">
         <f t="shared" si="9"/>
         <v>0.4909560723514213</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="10">
         <f t="shared" si="10"/>
         <v>0.2864359015260276</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="10">
         <f t="shared" si="12"/>
         <v>9.5622119815668205E-2</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="10">
         <f t="shared" si="13"/>
         <v>0.4352903535434331</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="11">
         <f t="shared" si="14"/>
         <v>0.25475179521911662</v>
       </c>
-      <c r="AC23">
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="18">
         <f t="shared" si="16"/>
         <v>1.6558935872333771</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="19">
         <f t="shared" si="17"/>
         <v>2.2959942316105058</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="2">
         <f t="shared" si="18"/>
         <v>1.6558935872333771</v>
       </c>
@@ -3360,100 +3614,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B24">
+    <row r="24" spans="1:33">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5">
         <v>178320</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="5">
         <v>49</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="5">
         <v>0.54500000000000004</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="5">
         <v>0.34899999999999998</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="5">
         <v>2</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="5">
         <v>-9.9309999999999992</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>4.7800000000000002E-2</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="5">
         <v>0.48099999999999998</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="5">
         <v>6.02E-5</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="5">
         <v>9.8500000000000004E-2</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="5">
         <v>0.34699999999999998</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="6">
         <v>79.168000000000006</v>
       </c>
-      <c r="P24">
+      <c r="O24" s="4"/>
+      <c r="P24" s="10">
         <f t="shared" si="15"/>
         <v>0.16907556457800207</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="10">
         <f t="shared" si="4"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="10">
         <f t="shared" si="5"/>
         <v>0.63061224489795931</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="10">
         <f t="shared" si="6"/>
         <v>0.35534798052887778</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="10">
         <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="10">
         <f t="shared" si="8"/>
         <v>0.40913674868898753</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="10">
         <f t="shared" si="9"/>
         <v>0.2868217054263566</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="10">
         <f t="shared" si="10"/>
         <v>0.50975700537034085</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="10">
         <f t="shared" si="11"/>
         <v>1E-3</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="10">
         <f t="shared" si="12"/>
         <v>7.7620967741935484E-2</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="10">
         <f t="shared" si="13"/>
         <v>0.39529675251959684</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="11">
         <f t="shared" si="14"/>
         <v>8.7898443130410675E-2</v>
       </c>
-      <c r="AC24">
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="18">
         <f t="shared" si="16"/>
         <v>1.1616363618348051</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="19">
         <f t="shared" si="17"/>
         <v>2.5612463150671747</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="2">
         <f t="shared" si="18"/>
         <v>1.1616363618348051</v>
       </c>
@@ -3466,100 +3723,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B25">
+    <row r="25" spans="1:33">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5">
         <v>201493</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="5">
         <v>49</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="5">
         <v>0.72599999999999998</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="5">
         <v>0.66700000000000004</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="5">
         <v>10</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="5">
         <v>-4.0720000000000001</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="5">
         <v>0.48199999999999998</v>
       </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
+      <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
         <v>4.4600000000000001E-2</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="6">
         <v>87.085999999999999</v>
       </c>
-      <c r="P25">
+      <c r="O25" s="4"/>
+      <c r="P25" s="10">
         <f t="shared" si="15"/>
         <v>0.27950363836509456</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="10">
         <f t="shared" si="4"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="10">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="10">
         <f t="shared" si="6"/>
         <v>0.77371398500197353</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="10">
         <f t="shared" si="7"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="10">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="10">
         <f t="shared" si="9"/>
         <v>0.30361757105943149</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="10">
         <f t="shared" si="10"/>
         <v>0.51082043919817099</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="10">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="10">
         <f t="shared" si="13"/>
         <v>0.16813309870420731</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="11">
         <f t="shared" si="14"/>
         <v>0.15665077669818611</v>
       </c>
-      <c r="AC25">
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="18">
         <f t="shared" si="16"/>
         <v>1.9983539355053765</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="19">
         <f t="shared" si="17"/>
         <v>2.282479453143786</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="2">
         <f t="shared" si="18"/>
         <v>1.9983539355053765</v>
       </c>
@@ -3572,100 +3832,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B26">
+    <row r="26" spans="1:33">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5">
         <v>224893</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="5">
         <v>50</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="5">
         <v>0.44400000000000001</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="5">
         <v>7.8899999999999998E-2</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="5">
         <v>11</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="5">
         <v>-13.848000000000001</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="5">
         <v>0.84</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="5">
         <v>1.64E-4</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="5">
         <v>0.106</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="5">
         <v>0.154</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="6">
         <v>87.347999999999999</v>
       </c>
-      <c r="P26">
+      <c r="O26" s="4"/>
+      <c r="P26" s="10">
         <f t="shared" si="15"/>
         <v>0.3910134526583654</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="10">
         <f t="shared" si="4"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="10">
         <f t="shared" si="5"/>
         <v>0.42448979591836739</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="10">
         <f t="shared" si="8"/>
         <v>1.4118596208148324E-2</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="10">
         <f t="shared" si="9"/>
         <v>0.26873385012919893</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="10">
         <f t="shared" si="10"/>
         <v>0.89152974956133357</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="10">
         <f t="shared" si="11"/>
         <v>2.7242524916943523E-3</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="10">
         <f t="shared" si="12"/>
         <v>8.8421658986175114E-2</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="10">
         <f t="shared" si="13"/>
         <v>8.6546152615581504E-2</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="11">
         <f t="shared" si="14"/>
         <v>0.1589257339341999</v>
       </c>
-      <c r="AC26">
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="18">
         <f t="shared" si="16"/>
         <v>1.531325350053653</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="19">
         <f t="shared" si="17"/>
         <v>2.6545789783670464</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="2">
         <f t="shared" si="18"/>
         <v>1.531325350053653</v>
       </c>
@@ -3678,100 +3941,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B27">
+    <row r="27" spans="1:33">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5">
         <v>221813</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="5">
         <v>49</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="5">
         <v>0.60199999999999998</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="5">
         <v>0.61899999999999999</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="5">
         <v>5</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="5">
         <v>-8.1940000000000008</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>3.56E-2</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="5">
         <v>7.7100000000000002E-2</v>
       </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="5">
         <v>0.22800000000000001</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="6">
         <v>107.428</v>
       </c>
-      <c r="P27">
+      <c r="O27" s="4"/>
+      <c r="P27" s="10">
         <f t="shared" si="15"/>
         <v>0.37633609248643057</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="10">
         <f t="shared" si="4"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="10">
         <f t="shared" si="5"/>
         <v>0.74693877551020404</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="10">
         <f t="shared" si="6"/>
         <v>0.71056439942112881</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="10">
         <f t="shared" si="7"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="10">
         <f t="shared" si="8"/>
         <v>0.5843081887858006</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="10">
         <f t="shared" si="9"/>
         <v>0.12919896640826872</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="10">
         <f t="shared" si="10"/>
         <v>8.0236082309778287E-2</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="10">
         <f t="shared" si="12"/>
         <v>6.3508064516129031E-2</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="10">
         <f t="shared" si="13"/>
         <v>0.20492721164613661</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="11">
         <f t="shared" si="14"/>
         <v>0.33328123507602003</v>
       </c>
-      <c r="AC27">
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="18">
         <f t="shared" si="16"/>
         <v>1.4202105495195843</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="19">
         <f t="shared" si="17"/>
         <v>2.4634658313574587</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="2">
         <f t="shared" si="18"/>
         <v>1.4202105495195843</v>
       </c>
@@ -3784,100 +4050,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B28">
+    <row r="28" spans="1:33">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5">
         <v>207600</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="5">
         <v>52</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="5">
         <v>0.36199999999999999</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="5">
         <v>0.54300000000000004</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="5">
         <v>5</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="5">
         <v>-7.069</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="5">
         <v>0.6</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="5">
         <v>3.2899999999999997E-4</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="5">
         <v>0.10100000000000001</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="5">
         <v>0.35399999999999998</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="6">
         <v>179.44300000000001</v>
       </c>
-      <c r="P28">
+      <c r="O28" s="4"/>
+      <c r="P28" s="10">
         <f t="shared" si="15"/>
         <v>0.30860579374496655</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="10">
         <f t="shared" si="4"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="10">
         <f t="shared" si="5"/>
         <v>0.25714285714285717</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="10">
         <f t="shared" si="6"/>
         <v>0.61057755558479154</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="10">
         <f t="shared" si="7"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="10">
         <f t="shared" si="8"/>
         <v>0.69776119402985071</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="10">
         <f t="shared" si="9"/>
         <v>0.16795865633074938</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="10">
         <f t="shared" si="10"/>
         <v>0.63630563088211833</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="10">
         <f t="shared" si="11"/>
         <v>5.4651162790697672E-3</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="10">
         <f t="shared" si="12"/>
         <v>8.1221198156682037E-2</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="10">
         <f t="shared" si="13"/>
         <v>0.40649496080627101</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="11">
         <f t="shared" si="14"/>
         <v>0.95859056847881796</v>
       </c>
-      <c r="AC28">
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="18">
         <f t="shared" si="16"/>
         <v>1.7033340397061014</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="19">
         <f t="shared" si="17"/>
         <v>2.2266152183238019</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="2">
         <f t="shared" si="18"/>
         <v>1.7033340397061014</v>
       </c>
@@ -3890,100 +4159,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B29">
+    <row r="29" spans="1:33">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5">
         <v>142840</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="5">
         <v>49</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="5">
         <v>0.58599999999999997</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="5">
         <v>0.70899999999999996</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="5">
         <v>11</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="5">
         <v>-5.24</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>5.4699999999999999E-2</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="5">
         <v>0.28199999999999997</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
         <v>0.16500000000000001</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="5">
         <v>0.45100000000000001</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="6">
         <v>93.296999999999997</v>
       </c>
-      <c r="P29">
+      <c r="O29" s="4"/>
+      <c r="P29" s="10">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="10">
         <f t="shared" si="4"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="10">
         <f t="shared" si="5"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="10">
         <f t="shared" si="6"/>
         <v>0.82896987238521247</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="10">
         <f t="shared" si="8"/>
         <v>0.88221056877773285</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="10">
         <f t="shared" si="9"/>
         <v>0.37596899224806202</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="10">
         <f t="shared" si="10"/>
         <v>0.29813367363215826</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="10">
         <f t="shared" si="12"/>
         <v>0.17338709677419356</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="10">
         <f t="shared" si="13"/>
         <v>0.56167013277875544</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="11">
         <f t="shared" si="14"/>
         <v>0.21058115606032976</v>
       </c>
-      <c r="AC29">
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="18">
         <f t="shared" si="16"/>
         <v>1.9183573797932514</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="19">
         <f t="shared" si="17"/>
         <v>2.2380874561626469</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="2">
         <f t="shared" si="18"/>
         <v>1.9183573797932514</v>
       </c>
@@ -3996,100 +4268,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B30">
+    <row r="30" spans="1:33">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5">
         <v>270426</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="5">
         <v>47</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="5">
         <v>0.55800000000000005</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="5">
         <v>0.39800000000000002</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="5">
         <v>5</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="5">
         <v>-7.5990000000000002</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <v>2.98E-2</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="5">
         <v>0.68100000000000005</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
+      <c r="J30" s="5">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5">
         <v>8.5900000000000004E-2</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="5">
         <v>0.183</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="6">
         <v>139.785</v>
       </c>
-      <c r="P30">
+      <c r="O30" s="4"/>
+      <c r="P30" s="10">
         <f t="shared" si="15"/>
         <v>0.60799534899236107</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="10">
         <f t="shared" si="4"/>
         <v>0.22580645161290322</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="10">
         <f t="shared" si="5"/>
         <v>0.65714285714285725</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="10">
         <f t="shared" si="6"/>
         <v>0.41981318247599009</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="10">
         <f t="shared" si="7"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="10">
         <f t="shared" si="8"/>
         <v>0.64431222267043153</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="10">
         <f t="shared" si="9"/>
         <v>5.4263565891472854E-2</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="10">
         <f t="shared" si="10"/>
         <v>0.72244377093635359</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="10">
         <f t="shared" si="12"/>
         <v>5.9475806451612906E-2</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="10">
         <f t="shared" si="13"/>
         <v>0.13293872980323149</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="11">
         <f t="shared" si="14"/>
         <v>0.61423845372372299</v>
       </c>
-      <c r="AC30">
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="18">
         <f t="shared" si="16"/>
         <v>1.6043207421232728</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="19">
         <f t="shared" si="17"/>
         <v>2.3211836108145745</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="2">
         <f t="shared" si="18"/>
         <v>1.6043207421232728</v>
       </c>
@@ -4102,100 +4377,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B31">
+    <row r="31" spans="1:33">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5">
         <v>303593</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="5">
         <v>51</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="5">
         <v>0.44400000000000001</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="5">
         <v>0.72899999999999998</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="5">
         <v>2</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="5">
         <v>-5.4420000000000002</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="5">
         <v>2.81E-2</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="5">
         <v>6.9499999999999996E-3</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="5">
         <v>1.7999999999999999E-6</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="5">
         <v>7.0300000000000001E-2</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="5">
         <v>0.38800000000000001</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="6">
         <v>95.257999999999996</v>
       </c>
-      <c r="P31">
+      <c r="O31" s="4"/>
+      <c r="P31" s="10">
         <f t="shared" si="15"/>
         <v>0.76604859731137442</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="10">
         <f t="shared" si="4"/>
         <v>0.35483870967741937</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="10">
         <f t="shared" si="5"/>
         <v>0.42448979591836739</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="10">
         <f t="shared" si="6"/>
         <v>0.85528219971056441</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="10">
         <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="10">
         <f t="shared" si="8"/>
         <v>0.86183945139169005</v>
       </c>
-      <c r="V31">
+      <c r="V31" s="10">
         <f t="shared" si="9"/>
         <v>3.2299741602067167E-2</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="10">
         <f t="shared" si="10"/>
         <v>5.6361992874993348E-3</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="10">
         <f t="shared" si="11"/>
         <v>2.9900332225913621E-5</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="10">
         <f t="shared" si="12"/>
         <v>3.7010368663594473E-2</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="10">
         <f t="shared" si="13"/>
         <v>0.46088625819868828</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="11">
         <f t="shared" si="14"/>
         <v>0.22760860315889098</v>
       </c>
-      <c r="AC31">
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="18">
         <f t="shared" si="16"/>
         <v>1.633074373714976</v>
       </c>
-      <c r="AD31">
+      <c r="AD31" s="19">
         <f t="shared" si="17"/>
         <v>2.5002711644826512</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="2">
         <f t="shared" si="18"/>
         <v>1.633074373714976</v>
       </c>
@@ -4208,100 +4486,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B32">
+    <row r="32" spans="1:33">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5">
         <v>230108</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="5">
         <v>47</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="5">
         <v>0.54200000000000004</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="5">
         <v>0.58399999999999996</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="5">
         <v>9</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="5">
         <v>-6.7839999999999998</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="5">
         <v>5.8700000000000002E-2</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="5">
         <v>0.38300000000000001</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="5">
         <v>3.2400000000000001E-5</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="5">
         <v>0.29699999999999999</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="5">
         <v>0.247</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="6">
         <v>91.647999999999996</v>
       </c>
-      <c r="P32">
+      <c r="O32" s="4"/>
+      <c r="P32" s="10">
         <f t="shared" si="15"/>
         <v>0.41586489204039134</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="10">
         <f t="shared" si="4"/>
         <v>0.22580645161290322</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="10">
         <f t="shared" si="5"/>
         <v>0.62448979591836751</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="10">
         <f t="shared" si="6"/>
         <v>0.66451782660176295</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="10">
         <f t="shared" si="8"/>
         <v>0.72650262202501004</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="10">
         <f t="shared" si="9"/>
         <v>0.42764857881136958</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="10">
         <f t="shared" si="10"/>
         <v>0.40554049024299471</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="10">
         <f t="shared" si="11"/>
         <v>5.3820598006644525E-4</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="10">
         <f t="shared" si="12"/>
         <v>0.363479262672811</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="10">
         <f t="shared" si="13"/>
         <v>0.23532234842425215</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="11">
         <f t="shared" si="14"/>
         <v>0.19626281834205977</v>
       </c>
-      <c r="AC32">
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="18">
         <f t="shared" si="16"/>
         <v>1.6810980692060249</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="19">
         <f t="shared" si="17"/>
         <v>2.1489021607743366</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="2">
         <f t="shared" si="18"/>
         <v>1.6810980692060249</v>
       </c>
@@ -4314,100 +4595,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B33">
+    <row r="33" spans="1:33">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5">
         <v>193373</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="5">
         <v>48</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="5">
         <v>0.44400000000000001</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="5">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="5">
         <v>8</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="5">
         <v>-5.6840000000000002</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="5">
         <v>3.9E-2</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="5">
         <v>0.28199999999999997</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="5">
         <v>1.4899999999999999E-6</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="5">
         <v>0.24399999999999999</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="6">
         <v>119.22</v>
       </c>
-      <c r="P33">
+      <c r="O33" s="4"/>
+      <c r="P33" s="10">
         <f t="shared" si="15"/>
         <v>0.24080877972999376</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="10">
         <f t="shared" si="4"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="10">
         <f t="shared" si="5"/>
         <v>0.42448979591836739</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="10">
         <f t="shared" si="6"/>
         <v>0.63031180107880558</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="10">
         <f t="shared" si="7"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="10">
         <f t="shared" si="8"/>
         <v>0.83743444937474765</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="10">
         <f t="shared" si="9"/>
         <v>0.1731266149870801</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="10">
         <f t="shared" si="10"/>
         <v>0.29813367363215826</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="10">
         <f t="shared" si="11"/>
         <v>2.4750830564784055E-5</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="10">
         <f t="shared" si="12"/>
         <v>8.2661290322580627E-2</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="10">
         <f t="shared" si="13"/>
         <v>0.2305231163013918</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="11">
         <f t="shared" si="14"/>
         <v>0.43567167678241164</v>
       </c>
-      <c r="AC33">
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="18">
         <f t="shared" si="16"/>
         <v>1.5168826295836715</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" s="19">
         <f t="shared" si="17"/>
         <v>2.3714734928337173</v>
       </c>
-      <c r="AE33">
+      <c r="AE33" s="2">
         <f t="shared" si="18"/>
         <v>1.5168826295836715</v>
       </c>
@@ -4420,100 +4704,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B34">
+    <row r="34" spans="1:33">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5">
         <v>222293</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="5">
         <v>47</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="5">
         <v>0.54300000000000004</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="5">
         <v>0.32700000000000001</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="5">
         <v>9</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="5">
         <v>-6.8129999999999997</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="5">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="5">
         <v>0.78500000000000003</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
         <v>8.8800000000000004E-2</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="5">
         <v>0.249</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="6">
         <v>135.25700000000001</v>
       </c>
-      <c r="P34">
+      <c r="O34" s="4"/>
+      <c r="P34" s="10">
         <f t="shared" si="15"/>
         <v>0.37862347329244639</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="10">
         <f t="shared" si="4"/>
         <v>0.22580645161290322</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="10">
         <f t="shared" si="5"/>
         <v>0.62653061224489803</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="10">
         <f t="shared" si="6"/>
         <v>0.32640442047099066</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="10">
         <f t="shared" si="7"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="10">
         <f t="shared" si="8"/>
         <v>0.72357805566760791</v>
       </c>
-      <c r="V34">
+      <c r="V34" s="10">
         <f t="shared" si="9"/>
         <v>0.14470284237726097</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="10">
         <f t="shared" si="10"/>
         <v>0.83304088903068019</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="10">
         <f t="shared" si="12"/>
         <v>6.3652073732718903E-2</v>
       </c>
-      <c r="Z34">
+      <c r="Z34" s="10">
         <f t="shared" si="13"/>
         <v>0.23852183650615905</v>
       </c>
-      <c r="AA34">
+      <c r="AA34" s="11">
         <f t="shared" si="14"/>
         <v>0.57492163553795805</v>
       </c>
-      <c r="AC34">
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="18">
         <f t="shared" si="16"/>
         <v>1.7299672272986877</v>
       </c>
-      <c r="AD34">
+      <c r="AD34" s="19">
         <f t="shared" si="17"/>
         <v>2.2549630573950932</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="2">
         <f t="shared" si="18"/>
         <v>1.7299672272986877</v>
       </c>
@@ -4526,100 +4813,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B35">
+    <row r="35" spans="1:33">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5">
         <v>220720</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="5">
         <v>46</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="5">
         <v>0.45700000000000002</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="5">
         <v>0.36599999999999999</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="5">
         <v>2</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="5">
         <v>-7.3780000000000001</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="5">
         <v>4.1300000000000003E-2</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="5">
         <v>0.79200000000000004</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="5">
         <v>3.0700000000000001E-5</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="5">
         <v>8.8099999999999998E-2</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="5">
         <v>0.26300000000000001</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="6">
         <v>141.36000000000001</v>
       </c>
-      <c r="P35">
+      <c r="O35" s="4"/>
+      <c r="P35" s="10">
         <f t="shared" si="15"/>
         <v>0.37112753577606544</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="10">
         <f t="shared" si="4"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="10">
         <f t="shared" si="5"/>
         <v>0.45102040816326538</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="10">
         <f t="shared" si="6"/>
         <v>0.37771345875542695</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="10">
         <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="10">
         <f t="shared" si="8"/>
         <v>0.66659943525615162</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="10">
         <f t="shared" si="9"/>
         <v>0.20284237726098195</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="10">
         <f t="shared" si="10"/>
         <v>0.84048492582549061</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="10">
         <f t="shared" si="11"/>
         <v>5.0996677740863794E-4</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="10">
         <f t="shared" si="12"/>
         <v>6.2644009216589858E-2</v>
       </c>
-      <c r="Z35">
+      <c r="Z35" s="10">
         <f t="shared" si="13"/>
         <v>0.26091825307950733</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="11">
         <f t="shared" si="14"/>
         <v>0.62791424626846248</v>
       </c>
-      <c r="AC35">
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="18">
         <f t="shared" si="16"/>
         <v>1.4874593297814147</v>
       </c>
-      <c r="AD35">
+      <c r="AD35" s="19">
         <f t="shared" si="17"/>
         <v>2.3954650669891144</v>
       </c>
-      <c r="AE35">
+      <c r="AE35" s="2">
         <f t="shared" si="18"/>
         <v>1.4874593297814147</v>
       </c>
@@ -4632,100 +4922,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B36">
+    <row r="36" spans="1:33">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5">
         <v>231693</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="5">
         <v>45</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="5">
         <v>0.42199999999999999</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="5">
         <v>0.47499999999999998</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="5">
         <v>11</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="5">
         <v>-5.9489999999999998</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="5">
         <v>3.6900000000000002E-2</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="5">
         <v>0.45500000000000002</v>
       </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
         <v>0.14399999999999999</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="5">
         <v>0.28899999999999998</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="6">
         <v>167.64699999999999</v>
       </c>
-      <c r="P36">
+      <c r="O36" s="4"/>
+      <c r="P36" s="10">
         <f t="shared" si="15"/>
         <v>0.4234180140769227</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="10">
         <f t="shared" si="4"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="10">
         <f t="shared" si="5"/>
         <v>0.37959183673469388</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="10">
         <f t="shared" si="6"/>
         <v>0.52111564267859489</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="10">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="10">
         <f t="shared" si="8"/>
         <v>0.81070996369503823</v>
       </c>
-      <c r="V36">
+      <c r="V36" s="10">
         <f t="shared" si="9"/>
         <v>0.1459948320413437</v>
       </c>
-      <c r="W36">
+      <c r="W36" s="10">
         <f t="shared" si="10"/>
         <v>0.48210772584675926</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" s="10">
         <f t="shared" si="12"/>
         <v>0.14314516129032256</v>
       </c>
-      <c r="Z36">
+      <c r="Z36" s="10">
         <f t="shared" si="13"/>
         <v>0.3025115981442969</v>
       </c>
-      <c r="AA36">
+      <c r="AA36" s="11">
         <f t="shared" si="14"/>
         <v>0.85616539460088392</v>
       </c>
-      <c r="AC36">
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="18">
         <f t="shared" si="16"/>
         <v>1.8376519912720193</v>
       </c>
-      <c r="AD36">
+      <c r="AD36" s="19">
         <f t="shared" si="17"/>
         <v>2.2192034286308715</v>
       </c>
-      <c r="AE36">
+      <c r="AE36" s="2">
         <f t="shared" si="18"/>
         <v>1.8376519912720193</v>
       </c>
@@ -4738,100 +5031,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B37">
+    <row r="37" spans="1:33">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5">
         <v>174933</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="5">
         <v>49</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="5">
         <v>0.57899999999999996</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="5">
         <v>0.621</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="5">
         <v>5</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="5">
         <v>-5.9340000000000002</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="5">
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="5">
         <v>0.27</v>
       </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
         <v>9.6500000000000002E-2</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="5">
         <v>0.61099999999999999</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="6">
         <v>139.38999999999999</v>
       </c>
-      <c r="P37">
+      <c r="O37" s="4"/>
+      <c r="P37" s="10">
         <f t="shared" si="15"/>
         <v>0.15293523376555299</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="10">
         <f t="shared" ref="Q37:Q55" si="21">(C37 - $C$1)/($C$2 - $C$1)</f>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="10">
         <f t="shared" ref="R37:R55" si="22">(D37 - $D$1)/($D$2 - $D$1)</f>
         <v>0.7</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="10">
         <f t="shared" ref="S37:S55" si="23">(E37 - $E$1)/($E$2- $E$1)</f>
         <v>0.71319563215366399</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="10">
         <f t="shared" ref="T37:T55" si="24">(F37 - $F$1)/($F$2- $F$1)</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="10">
         <f t="shared" ref="U37:U55" si="25">(G37 - $G$1)/($G$2- $G$1)</f>
         <v>0.81222267043162544</v>
       </c>
-      <c r="V37">
+      <c r="V37" s="10">
         <f t="shared" ref="V37:V55" si="26">(H37 - $H$1)/($H$2- $H$1)</f>
         <v>0.12532299741602063</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="10">
         <f t="shared" ref="W37:W55" si="27">(I37 - $I$1)/($I$2- $I$1)</f>
         <v>0.28537246769819752</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="10">
         <f t="shared" ref="X37:X55" si="28">(J37 - $J$1)/($J$2- $J$1)</f>
         <v>0</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="10">
         <f t="shared" ref="Y37:Y55" si="29">(K37 - $K$1)/($K$2- $K$1)</f>
         <v>7.4740783410138248E-2</v>
       </c>
-      <c r="Z37">
+      <c r="Z37" s="10">
         <f t="shared" ref="Z37:Z55" si="30">(L37 - $L$1)/($L$2- $L$1)</f>
         <v>0.81762917933130697</v>
       </c>
-      <c r="AA37">
+      <c r="AA37" s="11">
         <f t="shared" ref="AA37:AA55" si="31">(M37 - $M$1)/($M$2- $M$1)</f>
         <v>0.61080865178393107</v>
       </c>
-      <c r="AC37">
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="18">
         <f t="shared" si="16"/>
         <v>1.7654959078366099</v>
       </c>
-      <c r="AD37">
+      <c r="AD37" s="19">
         <f t="shared" si="17"/>
         <v>2.2456145034768791</v>
       </c>
-      <c r="AE37">
+      <c r="AE37" s="2">
         <f t="shared" si="18"/>
         <v>1.7654959078366099</v>
       </c>
@@ -4844,100 +5140,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B38">
+    <row r="38" spans="1:33">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5">
         <v>291533</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="5">
         <v>49</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="5">
         <v>0.41699999999999998</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="5">
         <v>0.63400000000000001</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="5">
         <v>9</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="5">
         <v>-7.181</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="5">
         <v>4.82E-2</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="5">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="5">
         <v>2.02E-5</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="5">
         <v>0.113</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="5">
         <v>0.32100000000000001</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="6">
         <v>152.65100000000001</v>
       </c>
-      <c r="P38">
+      <c r="O38" s="4"/>
+      <c r="P38" s="10">
         <f t="shared" si="15"/>
         <v>0.70857815456022721</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="10">
         <f t="shared" si="21"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="10">
         <f t="shared" si="22"/>
         <v>0.3693877551020408</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="10">
         <f t="shared" si="23"/>
         <v>0.73029864491514285</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="10">
         <f t="shared" si="24"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="10">
         <f t="shared" si="25"/>
         <v>0.68646631706333194</v>
       </c>
-      <c r="V38">
+      <c r="V38" s="10">
         <f t="shared" si="26"/>
         <v>0.29198966408268734</v>
       </c>
-      <c r="W38">
+      <c r="W38" s="10">
         <f t="shared" si="27"/>
         <v>1.6642739405540494E-2</v>
       </c>
-      <c r="X38">
+      <c r="X38" s="10">
         <f t="shared" si="28"/>
         <v>3.3554817275747512E-4</v>
       </c>
-      <c r="Y38">
+      <c r="Y38" s="10">
         <f t="shared" si="29"/>
         <v>9.8502304147465441E-2</v>
       </c>
-      <c r="Z38">
+      <c r="Z38" s="10">
         <f t="shared" si="30"/>
         <v>0.35370340745480727</v>
       </c>
-      <c r="AA38">
+      <c r="AA38" s="11">
         <f t="shared" si="31"/>
         <v>0.72595448348919411</v>
       </c>
-      <c r="AC38">
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="18">
         <f t="shared" si="16"/>
         <v>1.7731793175442365</v>
       </c>
-      <c r="AD38">
+      <c r="AD38" s="19">
         <f t="shared" si="17"/>
         <v>2.2278774781675712</v>
       </c>
-      <c r="AE38">
+      <c r="AE38" s="2">
         <f t="shared" si="18"/>
         <v>1.7731793175442365</v>
       </c>
@@ -4950,100 +5249,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B39">
+    <row r="39" spans="1:33">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5">
         <v>287346</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="5">
         <v>45</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="5">
         <v>0.53900000000000003</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="5">
         <v>0.187</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="5">
         <v>5</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="5">
         <v>-11.756</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="5">
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="5">
         <v>0.83299999999999996</v>
       </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
         <v>0.11899999999999999</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="5">
         <v>0.35599999999999998</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="6">
         <v>128.96899999999999</v>
       </c>
-      <c r="P39">
+      <c r="O39" s="4"/>
+      <c r="P39" s="10">
         <f t="shared" si="15"/>
         <v>0.68862552240441843</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="10">
         <f t="shared" si="21"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="10">
         <f t="shared" si="22"/>
         <v>0.6183673469387756</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="10">
         <f t="shared" si="23"/>
         <v>0.14221812919352717</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="10">
         <f t="shared" si="24"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U39">
+      <c r="U39" s="10">
         <f t="shared" si="25"/>
         <v>0.22509076240419515</v>
       </c>
-      <c r="V39">
+      <c r="V39" s="10">
         <f t="shared" si="26"/>
         <v>0.12532299741602063</v>
       </c>
-      <c r="W39">
+      <c r="W39" s="10">
         <f t="shared" si="27"/>
         <v>0.88408571276652315</v>
       </c>
-      <c r="X39">
+      <c r="X39" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y39">
+      <c r="Y39" s="10">
         <f t="shared" si="29"/>
         <v>0.10714285714285714</v>
       </c>
-      <c r="Z39">
+      <c r="Z39" s="10">
         <f t="shared" si="30"/>
         <v>0.40969444888817791</v>
       </c>
-      <c r="AA39">
+      <c r="AA39" s="11">
         <f t="shared" si="31"/>
         <v>0.52032266187362697</v>
       </c>
-      <c r="AC39">
+      <c r="AB39" s="2"/>
+      <c r="AC39" s="18">
         <f t="shared" si="16"/>
         <v>1.5516054520428109</v>
       </c>
-      <c r="AD39">
+      <c r="AD39" s="19">
         <f t="shared" si="17"/>
         <v>2.3945912065529122</v>
       </c>
-      <c r="AE39">
+      <c r="AE39" s="2">
         <f t="shared" si="18"/>
         <v>1.5516054520428109</v>
       </c>
@@ -5056,100 +5358,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B40">
+    <row r="40" spans="1:33">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5">
         <v>182186</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="5">
         <v>45</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="5">
         <v>0.55700000000000005</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="5">
         <v>0.185</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="5">
         <v>8</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="5">
         <v>-12.173999999999999</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="5">
         <v>4.3900000000000002E-2</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="5">
         <v>0.91300000000000003</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="5">
         <v>2.2200000000000001E-5</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="5">
         <v>0.15</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="5">
         <v>0.41799999999999998</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="6">
         <v>145.77199999999999</v>
       </c>
-      <c r="P40">
+      <c r="O40" s="4"/>
+      <c r="P40" s="10">
         <f t="shared" si="15"/>
         <v>0.18749851081978774</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="10">
         <f t="shared" si="21"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="10">
         <f t="shared" si="22"/>
         <v>0.65510204081632673</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="10">
         <f t="shared" si="23"/>
         <v>0.13958689646099198</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="10">
         <f t="shared" si="24"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="10">
         <f t="shared" si="25"/>
         <v>0.18293666801129488</v>
       </c>
-      <c r="V40">
+      <c r="V40" s="10">
         <f t="shared" si="26"/>
         <v>0.23643410852713179</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="10">
         <f t="shared" si="27"/>
         <v>0.96916041899292826</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="10">
         <f t="shared" si="28"/>
         <v>3.6877076411960134E-4</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" s="10">
         <f t="shared" si="29"/>
         <v>0.15178571428571427</v>
       </c>
-      <c r="Z40">
+      <c r="Z40" s="10">
         <f t="shared" si="30"/>
         <v>0.50887857942729164</v>
       </c>
-      <c r="AA40">
+      <c r="AA40" s="11">
         <f t="shared" si="31"/>
         <v>0.6662238314795037</v>
       </c>
-      <c r="AC40">
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="18">
         <f t="shared" si="16"/>
         <v>1.6712954664878252</v>
       </c>
-      <c r="AD40">
+      <c r="AD40" s="19">
         <f t="shared" si="17"/>
         <v>2.3706858411493141</v>
       </c>
-      <c r="AE40">
+      <c r="AE40" s="2">
         <f t="shared" si="18"/>
         <v>1.6712954664878252</v>
       </c>
@@ -5162,100 +5467,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B41">
+    <row r="41" spans="1:33">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5">
         <v>169920</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="5">
         <v>46</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="5">
         <v>0.40300000000000002</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="5">
         <v>0.59599999999999997</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="5">
         <v>2</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="5">
         <v>-6.7469999999999999</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="5">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="5">
         <v>0.255</v>
       </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
+      <c r="J41" s="5">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
         <v>0.307</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="5">
         <v>0.59399999999999997</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="6">
         <v>171.92</v>
       </c>
-      <c r="P41">
+      <c r="O41" s="4"/>
+      <c r="P41" s="10">
         <f t="shared" si="15"/>
         <v>0.12904640047272536</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="10">
         <f t="shared" si="21"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="10">
         <f t="shared" si="22"/>
         <v>0.34081632653061233</v>
       </c>
-      <c r="S41">
+      <c r="S41" s="10">
         <f t="shared" si="23"/>
         <v>0.68030522299697405</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="10">
         <f t="shared" si="24"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="U41">
+      <c r="U41" s="10">
         <f t="shared" si="25"/>
         <v>0.73023396530859208</v>
       </c>
-      <c r="V41">
+      <c r="V41" s="10">
         <f t="shared" si="26"/>
         <v>8.3979328165374623E-2</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="10">
         <f t="shared" si="27"/>
         <v>0.26942096028074658</v>
       </c>
-      <c r="X41">
+      <c r="X41" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" s="10">
         <f t="shared" si="29"/>
         <v>0.37788018433179715</v>
       </c>
-      <c r="Z41">
+      <c r="Z41" s="10">
         <f t="shared" si="30"/>
         <v>0.79043353063509836</v>
       </c>
-      <c r="AA41">
+      <c r="AA41" s="11">
         <f t="shared" si="31"/>
         <v>0.893268036850834</v>
       </c>
-      <c r="AC41">
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="18">
         <f t="shared" si="16"/>
         <v>1.6865737395499323</v>
       </c>
-      <c r="AD41">
+      <c r="AD41" s="19">
         <f t="shared" si="17"/>
         <v>2.3458537742075958</v>
       </c>
-      <c r="AE41">
+      <c r="AE41" s="2">
         <f t="shared" si="18"/>
         <v>1.6865737395499323</v>
       </c>
@@ -5268,100 +5576,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B42">
+    <row r="42" spans="1:33">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5">
         <v>156146</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="5">
         <v>43</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="5">
         <v>0.65</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="5">
         <v>0.188</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="5">
         <v>9</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="5">
         <v>-11.04</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="5">
         <v>0.88200000000000001</v>
       </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
+      <c r="J42" s="5">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
         <v>0.114</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="5">
         <v>0.254</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="6">
         <v>114.142</v>
       </c>
-      <c r="P42">
+      <c r="O42" s="4"/>
+      <c r="P42" s="10">
         <f t="shared" si="15"/>
         <v>6.340810209342998E-2</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="10">
         <f t="shared" si="21"/>
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="10">
         <f t="shared" si="22"/>
         <v>0.84489795918367361</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="10">
         <f t="shared" si="23"/>
         <v>0.14353374555979476</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="10">
         <f t="shared" si="24"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U42">
+      <c r="U42" s="10">
         <f t="shared" si="25"/>
         <v>0.29729729729729731</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="10">
         <f t="shared" si="26"/>
         <v>0.17571059431524547</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="10">
         <f t="shared" si="27"/>
         <v>0.93619397033019625</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="10">
         <f t="shared" si="29"/>
         <v>9.994239631336406E-2</v>
       </c>
-      <c r="Z42">
+      <c r="Z42" s="10">
         <f t="shared" si="30"/>
         <v>0.24652055671092629</v>
       </c>
-      <c r="AA42">
+      <c r="AA42" s="11">
         <f t="shared" si="31"/>
         <v>0.39157918500959477</v>
       </c>
-      <c r="AC42">
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="18">
         <f t="shared" si="16"/>
         <v>1.6239076293652632</v>
       </c>
-      <c r="AD42">
+      <c r="AD42" s="19">
         <f t="shared" si="17"/>
         <v>2.531599563837704</v>
       </c>
-      <c r="AE42">
+      <c r="AE42" s="2">
         <f t="shared" si="18"/>
         <v>1.6239076293652632</v>
       </c>
@@ -5374,100 +5685,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B43">
+    <row r="43" spans="1:33">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5">
         <v>286093</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="5">
         <v>46</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="5">
         <v>0.42399999999999999</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="5">
         <v>0.25900000000000001</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="5">
         <v>9</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="5">
         <v>-13.585000000000001</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="5">
         <v>4.4400000000000002E-2</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="5">
         <v>0.93600000000000005</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="5">
         <v>2.0899999999999999E-6</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="5">
         <v>0.73899999999999999</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="5">
         <v>0.48699999999999999</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="6">
         <v>69.045000000000002</v>
       </c>
-      <c r="P43">
+      <c r="O43" s="4"/>
+      <c r="P43" s="10">
         <f t="shared" si="15"/>
         <v>0.68265450542538131</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="10">
         <f t="shared" si="21"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="10">
         <f t="shared" si="22"/>
         <v>0.3836734693877551</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="10">
         <f t="shared" si="23"/>
         <v>0.23694250756479412</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="10">
         <f t="shared" si="24"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="U43">
+      <c r="U43" s="10">
         <f t="shared" si="25"/>
         <v>4.0641387656312894E-2</v>
       </c>
-      <c r="V43">
+      <c r="V43" s="10">
         <f t="shared" si="26"/>
         <v>0.24289405684754525</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="10">
         <f t="shared" si="27"/>
         <v>0.99361939703301971</v>
       </c>
-      <c r="X43">
+      <c r="X43" s="10">
         <f t="shared" si="28"/>
         <v>3.4717607973421925E-5</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" s="10">
         <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="Z43">
+      <c r="Z43" s="10">
         <f t="shared" si="30"/>
         <v>0.6192609182530795</v>
       </c>
-      <c r="AA43">
+      <c r="AA43" s="11">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AC43">
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="18">
         <f t="shared" si="16"/>
         <v>1.95132251563279</v>
       </c>
-      <c r="AD43">
+      <c r="AD43" s="19">
         <f t="shared" si="17"/>
         <v>2.3205079680765097</v>
       </c>
-      <c r="AE43">
+      <c r="AE43" s="2">
         <f t="shared" si="18"/>
         <v>1.95132251563279</v>
       </c>
@@ -5480,100 +5794,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B44">
+    <row r="44" spans="1:33">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5">
         <v>206268</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="5">
         <v>44</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="5">
         <v>0.68700000000000006</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="5">
         <v>0.79800000000000004</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="5">
         <v>3</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="5">
         <v>-5.548</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="5">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="5">
         <v>0.13900000000000001</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="5">
         <v>2.0999999999999999E-5</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="5">
         <v>8.9800000000000005E-2</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="5">
         <v>0.68</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="6">
         <v>118.68600000000001</v>
       </c>
-      <c r="P44">
+      <c r="O44" s="4"/>
+      <c r="P44" s="10">
         <f t="shared" si="15"/>
         <v>0.30225831200827269</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="10">
         <f t="shared" si="21"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="10">
         <f t="shared" si="22"/>
         <v>0.92040816326530628</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="10">
         <f t="shared" si="23"/>
         <v>0.94605972898302859</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="10">
         <f t="shared" si="24"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="U44">
+      <c r="U44" s="10">
         <f t="shared" si="25"/>
         <v>0.85114965711980628</v>
       </c>
-      <c r="V44">
+      <c r="V44" s="10">
         <f t="shared" si="26"/>
         <v>0.49224806201550403</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="10">
         <f t="shared" si="27"/>
         <v>0.14606263625245922</v>
       </c>
-      <c r="X44">
+      <c r="X44" s="10">
         <f t="shared" si="28"/>
         <v>3.4883720930232559E-4</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" s="10">
         <f t="shared" si="29"/>
         <v>6.5092165898617521E-2</v>
       </c>
-      <c r="Z44">
+      <c r="Z44" s="10">
         <f t="shared" si="30"/>
         <v>0.92801151815709493</v>
       </c>
-      <c r="AA44">
+      <c r="AA44" s="11">
         <f t="shared" si="31"/>
         <v>0.43103493188152864</v>
       </c>
-      <c r="AC44">
+      <c r="AB44" s="2"/>
+      <c r="AC44" s="18">
         <f t="shared" si="16"/>
         <v>1.9909549374766757</v>
       </c>
-      <c r="AD44">
+      <c r="AD44" s="19">
         <f t="shared" si="17"/>
         <v>2.2349573767518107</v>
       </c>
-      <c r="AE44">
+      <c r="AE44" s="2">
         <f t="shared" si="18"/>
         <v>1.9909549374766757</v>
       </c>
@@ -5586,100 +5903,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B45">
+    <row r="45" spans="1:33">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5">
         <v>151333</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="5">
         <v>41</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="5">
         <v>0.55500000000000005</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="5">
         <v>0.37</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="5">
         <v>10</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="5">
         <v>-9.827</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="5">
         <v>3.04E-2</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="5">
         <v>0.85099999999999998</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="5">
         <v>2.0599999999999999E-4</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="5">
         <v>0.129</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="5">
         <v>0.53300000000000003</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="6">
         <v>80.338999999999999</v>
       </c>
-      <c r="P45">
+      <c r="O45" s="4"/>
+      <c r="P45" s="10">
         <f t="shared" si="15"/>
         <v>4.0472344136442268E-2</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="10">
         <f t="shared" si="21"/>
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="10">
         <f t="shared" si="22"/>
         <v>0.65102040816326545</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="10">
         <f t="shared" si="23"/>
         <v>0.38297592422049731</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="10">
         <f t="shared" si="24"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="U45">
+      <c r="U45" s="10">
         <f t="shared" si="25"/>
         <v>0.41962484872932626</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="10">
         <f t="shared" si="26"/>
         <v>6.2015503875968978E-2</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="10">
         <f t="shared" si="27"/>
         <v>0.90322752166746423</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="10">
         <f t="shared" si="28"/>
         <v>3.4219269102990033E-3</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="10">
         <f t="shared" si="29"/>
         <v>0.12154377880184332</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="10">
         <f t="shared" si="30"/>
         <v>0.69284914413693821</v>
       </c>
-      <c r="AA45">
+      <c r="AA45" s="11">
         <f t="shared" si="31"/>
         <v>9.8066286349388257E-2</v>
       </c>
-      <c r="AC45">
+      <c r="AB45" s="2"/>
+      <c r="AC45" s="18">
         <f t="shared" si="16"/>
         <v>1.7028844440607467</v>
       </c>
-      <c r="AD45">
+      <c r="AD45" s="19">
         <f t="shared" si="17"/>
         <v>2.5033341983497004</v>
       </c>
-      <c r="AE45">
+      <c r="AE45" s="2">
         <f t="shared" si="18"/>
         <v>1.7028844440607467</v>
       </c>
@@ -5692,100 +6012,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B46">
+    <row r="46" spans="1:33">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5">
         <v>209051</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="5">
         <v>45</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="5">
         <v>0.41499999999999998</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="5">
         <v>0.59899999999999998</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="5">
         <v>2</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="5">
         <v>-5.891</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="5">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="5">
         <v>0.219</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="5">
         <v>1.11E-6</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="5">
         <v>0.32800000000000001</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="5">
         <v>0.55300000000000005</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="6">
         <v>172.709</v>
       </c>
-      <c r="P46">
+      <c r="O46" s="4"/>
+      <c r="P46" s="10">
         <f t="shared" si="15"/>
         <v>0.3155203553064852</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="10">
         <f t="shared" si="21"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="10">
         <f t="shared" si="22"/>
         <v>0.36530612244897959</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="10">
         <f t="shared" si="23"/>
         <v>0.68425207209577688</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="10">
         <f t="shared" si="24"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="U46">
+      <c r="U46" s="10">
         <f t="shared" si="25"/>
         <v>0.81655909640984259</v>
       </c>
-      <c r="V46">
+      <c r="V46" s="10">
         <f t="shared" si="26"/>
         <v>8.0103359173126623E-2</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="10">
         <f t="shared" si="27"/>
         <v>0.23113734247886425</v>
       </c>
-      <c r="X46">
+      <c r="X46" s="10">
         <f t="shared" si="28"/>
         <v>1.8438538205980066E-5</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" s="10">
         <f t="shared" si="29"/>
         <v>0.40812211981566815</v>
       </c>
-      <c r="Z46">
+      <c r="Z46" s="10">
         <f t="shared" si="30"/>
         <v>0.72484402495600719</v>
       </c>
-      <c r="AA46">
+      <c r="AA46" s="11">
         <f t="shared" si="31"/>
         <v>0.90011895768753214</v>
       </c>
-      <c r="AC46">
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="18">
         <f t="shared" si="16"/>
         <v>1.7288902266977622</v>
       </c>
-      <c r="AD46">
+      <c r="AD46" s="19">
         <f t="shared" si="17"/>
         <v>2.2914800084993994</v>
       </c>
-      <c r="AE46">
+      <c r="AE46" s="2">
         <f t="shared" si="18"/>
         <v>1.7288902266977622</v>
       </c>
@@ -5798,100 +6121,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B47">
+    <row r="47" spans="1:33">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5">
         <v>211600</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="5">
         <v>42</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="5">
         <v>0.56699999999999995</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="5">
         <v>0.66500000000000004</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="5">
         <v>11</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="5">
         <v>-4.4649999999999999</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="5">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="5">
         <v>7.1400000000000005E-2</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
         <v>0.17699999999999999</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="5">
         <v>0.59799999999999998</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="6">
         <v>97.814999999999998</v>
       </c>
-      <c r="P47">
+      <c r="O47" s="4"/>
+      <c r="P47" s="10">
         <f t="shared" si="15"/>
         <v>0.32766730046176501</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="10">
         <f t="shared" si="21"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="10">
         <f t="shared" si="22"/>
         <v>0.67551020408163254</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="10">
         <f t="shared" si="23"/>
         <v>0.77108275226943834</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="10">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="U47">
+      <c r="U47" s="10">
         <f t="shared" si="25"/>
         <v>0.96036708350141176</v>
       </c>
-      <c r="V47">
+      <c r="V47" s="10">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="10">
         <f t="shared" si="27"/>
         <v>7.4174509491146928E-2</v>
       </c>
-      <c r="X47">
+      <c r="X47" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" s="10">
         <f t="shared" si="29"/>
         <v>0.19066820276497695</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="10">
         <f t="shared" si="30"/>
         <v>0.79683250679891215</v>
       </c>
-      <c r="AA47">
+      <c r="AA47" s="11">
         <f t="shared" si="31"/>
         <v>0.24981114381723932</v>
       </c>
-      <c r="AC47">
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="18">
         <f t="shared" si="16"/>
         <v>1.9554845039801849</v>
       </c>
-      <c r="AD47">
+      <c r="AD47" s="19">
         <f t="shared" si="17"/>
         <v>2.3669938700531246</v>
       </c>
-      <c r="AE47">
+      <c r="AE47" s="2">
         <f t="shared" si="18"/>
         <v>1.9554845039801849</v>
       </c>
@@ -5904,100 +6230,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B48">
+    <row r="48" spans="1:33">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5">
         <v>309746</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="5">
         <v>45</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <v>0.32</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="5">
         <v>0.438</v>
       </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
+      <c r="F48" s="5">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5">
         <v>-7.5529999999999999</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="5">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="5">
         <v>0.70299999999999996</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="5">
         <v>1.26E-5</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="5">
         <v>0.10100000000000001</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="5">
         <v>0.46500000000000002</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="6">
         <v>184.21199999999999</v>
       </c>
-      <c r="P48">
+      <c r="O48" s="4"/>
+      <c r="P48" s="10">
         <f t="shared" si="15"/>
         <v>0.7953699600184897</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="10">
         <f t="shared" si="21"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="10">
         <f t="shared" si="22"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="10">
         <f t="shared" si="23"/>
         <v>0.47243783712669385</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="U48">
+      <c r="U48" s="10">
         <f t="shared" si="25"/>
         <v>0.64895118999596602</v>
       </c>
-      <c r="V48">
+      <c r="V48" s="10">
         <f t="shared" si="26"/>
         <v>0.81912144702842382</v>
       </c>
-      <c r="W48">
+      <c r="W48" s="10">
         <f t="shared" si="27"/>
         <v>0.7458393151486149</v>
       </c>
-      <c r="X48">
+      <c r="X48" s="10">
         <f t="shared" si="28"/>
         <v>2.0930232558139536E-4</v>
       </c>
-      <c r="Y48">
+      <c r="Y48" s="10">
         <f t="shared" si="29"/>
         <v>8.1221198156682037E-2</v>
       </c>
-      <c r="Z48">
+      <c r="Z48" s="10">
         <f t="shared" si="30"/>
         <v>0.58406654935210378</v>
       </c>
-      <c r="AA48">
+      <c r="AA48" s="11">
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="AC48">
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="18">
         <f t="shared" si="16"/>
         <v>1.9766936392417995</v>
       </c>
-      <c r="AD48">
+      <c r="AD48" s="19">
         <f t="shared" si="17"/>
         <v>2.2242855835291127</v>
       </c>
-      <c r="AE48">
+      <c r="AE48" s="2">
         <f t="shared" si="18"/>
         <v>1.9766936392417995</v>
       </c>
@@ -6010,100 +6339,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B49">
+    <row r="49" spans="1:33">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5">
         <v>200040</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="5">
         <v>43</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="5">
         <v>0.47899999999999998</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="5">
         <v>0.502</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="5">
         <v>6</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="5">
         <v>-5.1639999999999997</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="5">
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="5">
         <v>0.223</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
+      <c r="J49" s="5">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
         <v>7.9899999999999999E-2</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="5">
         <v>0.57799999999999996</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="6">
         <v>176.49</v>
       </c>
-      <c r="P49">
+      <c r="O49" s="4"/>
+      <c r="P49" s="10">
         <f t="shared" si="15"/>
         <v>0.27257954605021756</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="10">
         <f t="shared" si="21"/>
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="10">
         <f t="shared" si="22"/>
         <v>0.49591836734693878</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="10">
         <f t="shared" si="23"/>
         <v>0.55663728456782002</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="10">
         <f t="shared" si="24"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="U49">
+      <c r="U49" s="10">
         <f t="shared" si="25"/>
         <v>0.88987494957644209</v>
       </c>
-      <c r="V49">
+      <c r="V49" s="10">
         <f t="shared" si="26"/>
         <v>0.33979328165374678</v>
       </c>
-      <c r="W49">
+      <c r="W49" s="10">
         <f t="shared" si="27"/>
         <v>0.23539107779018453</v>
       </c>
-      <c r="X49">
+      <c r="X49" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y49">
+      <c r="Y49" s="10">
         <f t="shared" si="29"/>
         <v>5.0835253456221197E-2</v>
       </c>
-      <c r="Z49">
+      <c r="Z49" s="10">
         <f t="shared" si="30"/>
         <v>0.76483762597984317</v>
       </c>
-      <c r="AA49">
+      <c r="AA49" s="11">
         <f t="shared" si="31"/>
         <v>0.93294954283779219</v>
       </c>
-      <c r="AC49">
+      <c r="AB49" s="2"/>
+      <c r="AC49" s="18">
         <f t="shared" si="16"/>
         <v>1.8323938262545001</v>
       </c>
-      <c r="AD49">
+      <c r="AD49" s="19">
         <f t="shared" si="17"/>
         <v>2.2350784769155934</v>
       </c>
-      <c r="AE49">
+      <c r="AE49" s="2">
         <f t="shared" si="18"/>
         <v>1.8323938262545001</v>
       </c>
@@ -6116,100 +6448,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B50">
+    <row r="50" spans="1:33">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5">
         <v>345026</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="5">
         <v>44</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <v>0.38800000000000001</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="5">
         <v>0.57499999999999996</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="5">
         <v>5</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="5">
         <v>-7.2720000000000002</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="5">
         <v>2.93E-2</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="5">
         <v>0.26600000000000001</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="5">
         <v>2.2499999999999998E-3</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="5">
         <v>9.5600000000000004E-2</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="5">
         <v>0.218</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="6">
         <v>86.582999999999998</v>
       </c>
-      <c r="P50">
+      <c r="O50" s="4"/>
+      <c r="P50" s="10">
         <f t="shared" si="15"/>
         <v>0.96349244926065181</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="10">
         <f t="shared" si="21"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="R50">
+      <c r="R50" s="10">
         <f t="shared" si="22"/>
         <v>0.31020408163265312</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="10">
         <f t="shared" si="23"/>
         <v>0.65267727930535457</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="10">
         <f t="shared" si="24"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U50">
+      <c r="U50" s="10">
         <f t="shared" si="25"/>
         <v>0.67728922952803539</v>
       </c>
-      <c r="V50">
+      <c r="V50" s="10">
         <f t="shared" si="26"/>
         <v>4.7803617571059415E-2</v>
       </c>
-      <c r="W50">
+      <c r="W50" s="10">
         <f t="shared" si="27"/>
         <v>0.28111873238687729</v>
       </c>
-      <c r="X50">
+      <c r="X50" s="10">
         <f t="shared" si="28"/>
         <v>3.7375415282392029E-2</v>
       </c>
-      <c r="Y50">
+      <c r="Y50" s="10">
         <f t="shared" si="29"/>
         <v>7.3444700460829501E-2</v>
       </c>
-      <c r="Z50">
+      <c r="Z50" s="10">
         <f t="shared" si="30"/>
         <v>0.18892977123660215</v>
       </c>
-      <c r="AA50">
+      <c r="AA50" s="11">
         <f t="shared" si="31"/>
         <v>0.15228320612675506</v>
       </c>
-      <c r="AC50">
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="18">
         <f t="shared" si="16"/>
         <v>1.5098020081593098</v>
       </c>
-      <c r="AD50">
+      <c r="AD50" s="19">
         <f t="shared" si="17"/>
         <v>2.5185530991105831</v>
       </c>
-      <c r="AE50">
+      <c r="AE50" s="2">
         <f t="shared" si="18"/>
         <v>1.5098020081593098</v>
       </c>
@@ -6222,100 +6557,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B51">
+    <row r="51" spans="1:33">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5">
         <v>159173</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>40</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="5">
         <v>0.57199999999999995</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="5">
         <v>0.191</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="5">
         <v>11</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="5">
         <v>-10.545</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="5">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="5">
         <v>0.94</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="5">
         <v>6.2500000000000001E-5</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="5">
         <v>0.221</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="5">
         <v>0.48399999999999999</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="6">
         <v>139.797</v>
       </c>
-      <c r="P51">
+      <c r="O51" s="4"/>
+      <c r="P51" s="10">
         <f t="shared" si="15"/>
         <v>7.7832897301367193E-2</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="10">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="10">
         <f t="shared" si="22"/>
         <v>0.68571428571428561</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="10">
         <f t="shared" si="23"/>
         <v>0.14748059465859756</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="10">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="U51">
+      <c r="U51" s="10">
         <f t="shared" si="25"/>
         <v>0.34721661960467926</v>
       </c>
-      <c r="V51">
+      <c r="V51" s="10">
         <f t="shared" si="26"/>
         <v>0.16020671834625322</v>
       </c>
-      <c r="W51">
+      <c r="W51" s="10">
         <f t="shared" si="27"/>
         <v>0.99787313234433983</v>
       </c>
-      <c r="X51">
+      <c r="X51" s="10">
         <f t="shared" si="28"/>
         <v>1.0382059800664453E-3</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="10">
         <f t="shared" si="29"/>
         <v>0.25403225806451613</v>
       </c>
-      <c r="Z51">
+      <c r="Z51" s="10">
         <f t="shared" si="30"/>
         <v>0.61446168613021912</v>
       </c>
-      <c r="AA51">
+      <c r="AA51" s="11">
         <f t="shared" si="31"/>
         <v>0.61434265023834955</v>
       </c>
-      <c r="AC51">
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="18">
         <f t="shared" si="16"/>
         <v>1.8599737769002005</v>
       </c>
-      <c r="AD51">
+      <c r="AD51" s="19">
         <f t="shared" si="17"/>
         <v>2.3788872091780746</v>
       </c>
-      <c r="AE51">
+      <c r="AE51" s="2">
         <f t="shared" si="18"/>
         <v>1.8599737769002005</v>
       </c>
@@ -6328,100 +6666,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B52">
+    <row r="52" spans="1:33">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5">
         <v>346397</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="5">
         <v>45</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="5">
         <v>0.28799999999999998</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="5">
         <v>0.18</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="5">
         <v>7</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="5">
         <v>-10.987</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="5">
         <v>4.0300000000000002E-2</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="5">
         <v>0.90500000000000003</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
+      <c r="J52" s="5">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
         <v>0.159</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="5">
         <v>0.20200000000000001</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="6">
         <v>88.054000000000002</v>
       </c>
-      <c r="P52">
+      <c r="O52" s="4"/>
+      <c r="P52" s="10">
         <f t="shared" si="15"/>
         <v>0.97002578068783452</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="10">
         <f t="shared" si="21"/>
         <v>0.16129032258064516</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="10">
         <f t="shared" si="22"/>
         <v>0.10612244897959182</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="10">
         <f t="shared" si="23"/>
         <v>0.133008814629654</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="10">
         <f t="shared" si="24"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U52">
+      <c r="U52" s="10">
         <f t="shared" si="25"/>
         <v>0.30264219443323914</v>
       </c>
-      <c r="V52">
+      <c r="V52" s="10">
         <f t="shared" si="26"/>
         <v>0.18992248062015507</v>
       </c>
-      <c r="W52">
+      <c r="W52" s="10">
         <f t="shared" si="27"/>
         <v>0.9606529483702877</v>
       </c>
-      <c r="X52">
+      <c r="X52" s="10">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="Y52">
+      <c r="Y52" s="10">
         <f t="shared" si="29"/>
         <v>0.16474654377880185</v>
       </c>
-      <c r="Z52">
+      <c r="Z52" s="10">
         <f t="shared" si="30"/>
         <v>0.16333386658134699</v>
       </c>
-      <c r="AA52">
+      <c r="AA52" s="11">
         <f t="shared" si="31"/>
         <v>0.16505596221139737</v>
       </c>
-      <c r="AC52">
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="18">
         <f t="shared" si="16"/>
         <v>1.5913693348872802</v>
       </c>
-      <c r="AD52">
+      <c r="AD52" s="19">
         <f t="shared" si="17"/>
         <v>2.574126329756643</v>
       </c>
-      <c r="AE52">
+      <c r="AE52" s="2">
         <f t="shared" si="18"/>
         <v>1.5913693348872802</v>
       </c>
@@ -6434,100 +6775,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B53">
+    <row r="53" spans="1:33">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5">
         <v>247133</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="5">
         <v>42</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="5">
         <v>0.40600000000000003</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="5">
         <v>0.34100000000000003</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="5">
         <v>7</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="5">
         <v>-7.7469999999999999</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="5">
         <v>3.49E-2</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="5">
         <v>0.68100000000000005</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="5">
         <v>5.6800000000000004E-4</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="5">
         <v>7.8899999999999998E-2</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="5">
         <v>0.28599999999999998</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="6">
         <v>148.654</v>
       </c>
-      <c r="P53">
+      <c r="O53" s="4"/>
+      <c r="P53" s="10">
         <f t="shared" si="15"/>
         <v>0.49699543000376467</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="10">
         <f t="shared" si="21"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="10">
         <f t="shared" si="22"/>
         <v>0.34693877551020419</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="10">
         <f t="shared" si="23"/>
         <v>0.344823049598737</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="10">
         <f t="shared" si="24"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U53">
+      <c r="U53" s="10">
         <f t="shared" si="25"/>
         <v>0.62938684953610324</v>
       </c>
-      <c r="V53">
+      <c r="V53" s="10">
         <f t="shared" si="26"/>
         <v>0.12015503875968991</v>
       </c>
-      <c r="W53">
+      <c r="W53" s="10">
         <f t="shared" si="27"/>
         <v>0.72244377093635359</v>
       </c>
-      <c r="X53">
+      <c r="X53" s="10">
         <f t="shared" si="28"/>
         <v>9.4352159468438553E-3</v>
       </c>
-      <c r="Y53">
+      <c r="Y53" s="10">
         <f t="shared" si="29"/>
         <v>4.9395161290322578E-2</v>
       </c>
-      <c r="Z53">
+      <c r="Z53" s="10">
         <f t="shared" si="30"/>
         <v>0.29771236602143658</v>
       </c>
-      <c r="AA53">
+      <c r="AA53" s="11">
         <f t="shared" si="31"/>
         <v>0.69124836107565535</v>
       </c>
-      <c r="AC53">
+      <c r="AB53" s="2"/>
+      <c r="AC53" s="18">
         <f t="shared" si="16"/>
         <v>1.5481830680597051</v>
       </c>
-      <c r="AD53">
+      <c r="AD53" s="19">
         <f t="shared" si="17"/>
         <v>2.3617881454687568</v>
       </c>
-      <c r="AE53">
+      <c r="AE53" s="2">
         <f t="shared" si="18"/>
         <v>1.5481830680597051</v>
       </c>
@@ -6540,100 +6884,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B54">
+    <row r="54" spans="1:33">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5">
         <v>206636</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="5">
         <v>42</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="5">
         <v>0.68400000000000005</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="5">
         <v>0.53600000000000003</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="5">
         <v>5</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="5">
         <v>-7.6349999999999998</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="5">
         <v>4.02E-2</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="5">
         <v>1.65E-3</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="5">
         <v>6.0199999999999997E-2</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="5">
         <v>0.106</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="5">
         <v>0.40899999999999997</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="6">
         <v>107.98099999999999</v>
       </c>
-      <c r="P54">
+      <c r="O54" s="4"/>
+      <c r="P54" s="10">
         <f t="shared" si="15"/>
         <v>0.30401197062621815</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="10">
         <f t="shared" si="21"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="10">
         <f t="shared" si="22"/>
         <v>0.91428571428571448</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="10">
         <f t="shared" si="23"/>
         <v>0.60136824102091835</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="10">
         <f t="shared" si="24"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="U54">
+      <c r="U54" s="10">
         <f t="shared" si="25"/>
         <v>0.64068172650262201</v>
       </c>
-      <c r="V54">
+      <c r="V54" s="10">
         <f t="shared" si="26"/>
         <v>0.18863049095607234</v>
       </c>
-      <c r="W54">
+      <c r="W54" s="10">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="X54">
+      <c r="X54" s="10">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="Y54">
+      <c r="Y54" s="10">
         <f t="shared" si="29"/>
         <v>8.8421658986175114E-2</v>
       </c>
-      <c r="Z54">
+      <c r="Z54" s="10">
         <f t="shared" si="30"/>
         <v>0.49448088305871057</v>
       </c>
-      <c r="AA54">
+      <c r="AA54" s="11">
         <f t="shared" si="31"/>
         <v>0.33808295779172853</v>
       </c>
-      <c r="AC54">
+      <c r="AB54" s="2"/>
+      <c r="AC54" s="18">
         <f t="shared" si="16"/>
         <v>1.8202866984964519</v>
       </c>
-      <c r="AD54">
+      <c r="AD54" s="19">
         <f t="shared" si="17"/>
         <v>2.2661405982664373</v>
       </c>
-      <c r="AE54">
+      <c r="AE54" s="2">
         <f t="shared" si="18"/>
         <v>1.8202866984964519</v>
       </c>
@@ -6646,100 +6993,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B55">
+    <row r="55" spans="1:33" ht="15" thickBot="1">
+      <c r="A55" s="7"/>
+      <c r="B55" s="8">
         <v>276146</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="8">
         <v>40</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="8">
         <v>0.46300000000000002</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="8">
         <v>0.248</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="8">
         <v>10</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="8">
         <v>-10.246</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="8">
         <v>4.48E-2</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="8">
         <v>0.871</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="8">
         <v>2.83E-5</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="8">
         <v>0.10299999999999999</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="8">
         <v>0.18099999999999999</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="9">
         <v>139.31</v>
       </c>
-      <c r="P55">
+      <c r="O55" s="7"/>
+      <c r="P55" s="12">
         <f t="shared" si="15"/>
         <v>0.63525330359738286</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="12">
         <f t="shared" si="22"/>
         <v>0.46326530612244904</v>
       </c>
-      <c r="S55">
+      <c r="S55" s="12">
         <f t="shared" si="23"/>
         <v>0.22247072753585054</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="12">
         <f t="shared" si="24"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="U55">
+      <c r="U55" s="12">
         <f t="shared" si="25"/>
         <v>0.37736990722065339</v>
       </c>
-      <c r="V55">
+      <c r="V55" s="12">
         <f t="shared" si="26"/>
         <v>0.24806201550387597</v>
       </c>
-      <c r="W55">
+      <c r="W55" s="12">
         <f t="shared" si="27"/>
         <v>0.92449619822406559</v>
       </c>
-      <c r="X55">
+      <c r="X55" s="12">
         <f t="shared" si="28"/>
         <v>4.7009966777408643E-4</v>
       </c>
-      <c r="Y55">
+      <c r="Y55" s="12">
         <f t="shared" si="29"/>
         <v>8.4101382488479245E-2</v>
       </c>
-      <c r="Z55">
+      <c r="Z55" s="12">
         <f t="shared" si="30"/>
         <v>0.12973924172132459</v>
       </c>
-      <c r="AA55">
+      <c r="AA55" s="13">
         <f t="shared" si="31"/>
         <v>0.61011400835308738</v>
       </c>
-      <c r="AC55">
+      <c r="AB55" s="2"/>
+      <c r="AC55" s="18">
         <f t="shared" si="16"/>
         <v>1.7172308166620376</v>
       </c>
-      <c r="AD55">
+      <c r="AD55" s="19">
         <f t="shared" si="17"/>
         <v>2.3958329404701959</v>
       </c>
-      <c r="AE55">
+      <c r="AE55" s="2">
         <f t="shared" si="18"/>
         <v>1.7172308166620376</v>
       </c>
@@ -6752,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33">
       <c r="AE56">
         <f>SUM(AE5:AE55)</f>
         <v>86.929696532993802</v>
@@ -6762,20 +7112,28 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="P58" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="Q59" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="AF5:AF55">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF5:AF55">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG5:AG55">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG5:AG55">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
+++ b/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ran\Programas\GitHub\Repositorios\Semestre-EneJun2026\Minería de datos\Práctica 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Práctica 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28D33F2-0CFA-42CA-B01F-BB7D7C17B6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clustering" sheetId="1" r:id="rId1"/>
     <sheet name="Medoides" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="33">
   <si>
     <t>MIN:</t>
   </si>
@@ -117,15 +131,18 @@
   <si>
     <t>Centroides</t>
   </si>
+  <si>
+    <t>PENDIENTE: Quitar el objeto separado de clústering</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -851,6 +868,7 @@
     <xf numFmtId="164" fontId="0" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -860,7 +878,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -881,7 +898,7 @@
     <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Buena" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
@@ -906,347 +923,7 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="66">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB3B3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1802,63 +1479,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BY57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="29.8984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.19921875" customWidth="1"/>
-    <col min="35" max="36" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.3984375" customWidth="1"/>
-    <col min="38" max="38" width="13.296875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.21875" customWidth="1"/>
+    <col min="35" max="36" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.44140625" customWidth="1"/>
+    <col min="38" max="38" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="15" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.69921875" customWidth="1"/>
-    <col min="44" max="44" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.296875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="50" max="51" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.296875" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.6640625" customWidth="1"/>
+    <col min="44" max="44" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="13" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="15.296875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="16.296875" customWidth="1"/>
-    <col min="69" max="69" width="13.59765625" customWidth="1"/>
-    <col min="70" max="73" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="15.296875" customWidth="1"/>
-    <col min="78" max="79" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16.33203125" customWidth="1"/>
+    <col min="69" max="69" width="13.5546875" customWidth="1"/>
+    <col min="70" max="73" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="15.33203125" customWidth="1"/>
+    <col min="78" max="79" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" ht="29.4" customHeight="1" thickBot="1">
-      <c r="AC1" s="37" t="s">
+    <row r="1" spans="1:73" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC1" s="38" t="s">
         <v>17</v>
       </c>
       <c r="AD1" s="20" t="s">
@@ -1900,7 +1577,7 @@
       <c r="AP1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="AS1" s="37" t="s">
+      <c r="AS1" s="38" t="s">
         <v>17</v>
       </c>
       <c r="AT1" s="20" t="s">
@@ -1942,7 +1619,7 @@
       <c r="BF1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="BH1" s="37" t="s">
+      <c r="BH1" s="38" t="s">
         <v>17</v>
       </c>
       <c r="BI1" s="20" t="s">
@@ -1985,7 +1662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:73" ht="14.4" customHeight="1">
+    <row r="2" spans="1:73" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2088,7 +1765,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC2" s="38"/>
+      <c r="AC2" s="39"/>
       <c r="AD2" s="23" t="s">
         <v>19</v>
       </c>
@@ -2140,7 +1817,7 @@
         <f t="shared" si="2"/>
         <v>0.43308656125452605</v>
       </c>
-      <c r="AS2" s="38"/>
+      <c r="AS2" s="39"/>
       <c r="AT2" s="23" t="s">
         <v>19</v>
       </c>
@@ -2192,7 +1869,7 @@
         <f t="shared" si="3"/>
         <v>0.44174829247961661</v>
       </c>
-      <c r="BH2" s="38"/>
+      <c r="BH2" s="39"/>
       <c r="BI2" s="23" t="s">
         <v>19</v>
       </c>
@@ -2245,7 +1922,7 @@
         <v>0.44192152710411842</v>
       </c>
     </row>
-    <row r="3" spans="1:73">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2348,7 +2025,7 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="AC3" s="39"/>
+      <c r="AC3" s="40"/>
       <c r="AD3" s="26" t="s">
         <v>20</v>
       </c>
@@ -2400,7 +2077,7 @@
         <f t="shared" si="7"/>
         <v>0.87432453162219514</v>
       </c>
-      <c r="AS3" s="39"/>
+      <c r="AS3" s="40"/>
       <c r="AT3" s="26" t="s">
         <v>20</v>
       </c>
@@ -2452,7 +2129,7 @@
         <f t="shared" si="8"/>
         <v>0.87432453162219514</v>
       </c>
-      <c r="BH3" s="39"/>
+      <c r="BH3" s="40"/>
       <c r="BI3" s="26" t="s">
         <v>20</v>
       </c>
@@ -2505,14 +2182,14 @@
         <v>0.2914415105407317</v>
       </c>
     </row>
-    <row r="4" spans="1:73" ht="14.4" thickBot="1">
+    <row r="4" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="M4" s="4"/>
       <c r="O4" s="3"/>
       <c r="AA4" s="4"/>
       <c r="AI4" s="19"/>
     </row>
-    <row r="5" spans="1:73">
+    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" t="s">
         <v>2</v>
@@ -2639,7 +2316,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:73">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6">
         <v>265306</v>
@@ -2868,7 +2545,7 @@
         <v>0.69780849999858741</v>
       </c>
     </row>
-    <row r="7" spans="1:73">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7">
         <v>268653</v>
@@ -3065,7 +2742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:73">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8">
         <v>231000</v>
@@ -3226,7 +2903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:73">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9">
         <v>238493</v>
@@ -3378,7 +3055,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:73">
+    <row r="10" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10">
         <v>230098</v>
@@ -3530,7 +3207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:73">
+    <row r="11" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11">
         <v>214666</v>
@@ -3679,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:73">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12">
         <v>209906</v>
@@ -3840,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:73">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13">
         <v>279373</v>
@@ -3989,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:73">
+    <row r="14" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14">
         <v>206267</v>
@@ -4138,7 +3815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:73">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15">
         <v>152946</v>
@@ -4287,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:73">
+    <row r="16" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16">
         <v>212480</v>
@@ -4436,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:64">
+    <row r="17" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17">
         <v>241146</v>
@@ -4585,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:64">
+    <row r="18" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18">
         <v>185228</v>
@@ -4734,7 +4411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:64">
+    <row r="19" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19">
         <v>259558</v>
@@ -4883,7 +4560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:64">
+    <row r="20" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20">
         <v>185421</v>
@@ -5032,7 +4709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:64">
+    <row r="21" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21">
         <v>211674</v>
@@ -5181,7 +4858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:64">
+    <row r="22" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22">
         <v>196973</v>
@@ -5330,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:64">
+    <row r="23" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23">
         <v>352687</v>
@@ -5479,7 +5156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:64">
+    <row r="24" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24">
         <v>213732</v>
@@ -5628,7 +5305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:64">
+    <row r="25" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25">
         <v>178320</v>
@@ -5777,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:64">
+    <row r="26" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26">
         <v>201493</v>
@@ -5926,7 +5603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:64">
+    <row r="27" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27">
         <v>224893</v>
@@ -6075,7 +5752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:64">
+    <row r="28" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28">
         <v>221813</v>
@@ -6224,7 +5901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:64">
+    <row r="29" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29">
         <v>207600</v>
@@ -6373,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:64">
+    <row r="30" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30">
         <v>142840</v>
@@ -6522,7 +6199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:64">
+    <row r="31" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31">
         <v>270426</v>
@@ -6671,7 +6348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:64">
+    <row r="32" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32">
         <v>303593</v>
@@ -6820,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:64">
+    <row r="33" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33">
         <v>230108</v>
@@ -6969,7 +6646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:64">
+    <row r="34" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34">
         <v>193373</v>
@@ -7118,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:64">
+    <row r="35" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35">
         <v>222293</v>
@@ -7267,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:64">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36">
         <v>220720</v>
@@ -7416,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:64">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37">
         <v>231693</v>
@@ -7565,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:64">
+    <row r="38" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38">
         <v>174933</v>
@@ -7738,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:64">
+    <row r="39" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39">
         <v>291533</v>
@@ -7887,7 +7564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:64">
+    <row r="40" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40">
         <v>287346</v>
@@ -8036,7 +7713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:64">
+    <row r="41" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41">
         <v>182186</v>
@@ -8185,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:64">
+    <row r="42" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42">
         <v>169920</v>
@@ -8334,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:64">
+    <row r="43" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43">
         <v>156146</v>
@@ -8483,7 +8160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:64">
+    <row r="44" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44">
         <v>286093</v>
@@ -8632,7 +8309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:64">
+    <row r="45" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45">
         <v>206268</v>
@@ -8781,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:64">
+    <row r="46" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46">
         <v>151333</v>
@@ -8930,7 +8607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:64">
+    <row r="47" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47">
         <v>209051</v>
@@ -9079,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:64">
+    <row r="48" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48">
         <v>211600</v>
@@ -9228,7 +8905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:77">
+    <row r="49" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49">
         <v>309746</v>
@@ -9377,7 +9054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:77">
+    <row r="50" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50">
         <v>200040</v>
@@ -9526,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:77">
+    <row r="51" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51">
         <v>345026</v>
@@ -9675,7 +9352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:77">
+    <row r="52" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52">
         <v>159173</v>
@@ -9824,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:77">
+    <row r="53" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53">
         <v>346397</v>
@@ -9973,7 +9650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:77">
+    <row r="54" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54">
         <v>247133</v>
@@ -10122,7 +9799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:77">
+    <row r="55" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55">
         <v>206636</v>
@@ -10271,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:77" ht="14.4" thickBot="1">
+    <row r="56" spans="1:77" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56">
         <v>276146</v>
@@ -10420,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:77">
+    <row r="57" spans="1:77" x14ac:dyDescent="0.3">
       <c r="AE57">
         <f>SUM(AE6:AE56)</f>
         <v>86.929696532993802</v>
@@ -10464,50 +10141,50 @@
     <mergeCell ref="BH1:BH3"/>
   </mergeCells>
   <conditionalFormatting sqref="AF6:AG56 AG57">
-    <cfRule type="cellIs" dxfId="65" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="19" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV6:AW57">
-    <cfRule type="cellIs" dxfId="63" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="17" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ6:BJ56">
-    <cfRule type="cellIs" dxfId="61" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>$BP$6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
       <formula>$BN$6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BK6:BL56 BK57">
-    <cfRule type="cellIs" dxfId="59" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN6">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$BP$6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$BN$6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BP5:BP6">
-    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$BP$6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$BN$6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10517,17 +10194,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B5:BE83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="11" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:57" ht="14.4" thickBot="1"/>
-    <row r="6" spans="3:57">
+    <row r="5" spans="3:57" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
@@ -10568,7 +10245,7 @@
         <v>0.57492163553795805</v>
       </c>
     </row>
-    <row r="7" spans="3:57">
+    <row r="7" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
@@ -10609,11 +10286,11 @@
         <v>0.89401477853899125</v>
       </c>
     </row>
-    <row r="8" spans="3:57">
+    <row r="8" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C8" s="3"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="3:57">
+    <row r="9" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C9" s="3"/>
       <c r="D9" t="s">
         <v>2</v>
@@ -10697,7 +10374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="3:57">
+    <row r="10" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C10" s="3"/>
       <c r="D10" s="1">
         <v>0.58359662039485916</v>
@@ -11044,7 +10721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:57">
+    <row r="11" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C11" s="3"/>
       <c r="D11" s="1">
         <v>0.59954633614014019</v>
@@ -11295,7 +10972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:57">
+    <row r="12" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
       <c r="D12" s="1">
         <v>0.42011560803823739</v>
@@ -11474,7 +11151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:57">
+    <row r="13" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C13" s="3"/>
       <c r="D13" s="1">
         <v>0.45582257549548005</v>
@@ -11653,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:57">
+    <row r="14" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C14" s="3"/>
       <c r="D14" s="1">
         <v>0.41581723827359934</v>
@@ -11832,7 +11509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:57">
+    <row r="15" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C15" s="3"/>
       <c r="D15" s="1">
         <v>0.34227794536019102</v>
@@ -12011,7 +11688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:57">
+    <row r="16" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C16" s="3"/>
       <c r="D16" s="1">
         <v>0.31959475236720086</v>
@@ -12190,7 +11867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:57">
+    <row r="17" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C17" s="3"/>
       <c r="D17" s="1">
         <v>0.65063117414116001</v>
@@ -12369,7 +12046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:57">
+    <row r="18" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
       <c r="D18" s="1">
         <v>0.30225354663159348</v>
@@ -12548,7 +12225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:57">
+    <row r="19" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C19" s="3"/>
       <c r="D19" s="1">
         <v>4.8158896719991233E-2</v>
@@ -12727,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:57">
+    <row r="20" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C20" s="3"/>
       <c r="D20" s="1">
         <v>0.33186083193946064</v>
@@ -12906,7 +12583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:57">
+    <row r="21" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C21" s="3"/>
       <c r="D21" s="1">
         <v>0.46846511982539663</v>
@@ -13085,7 +12762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:57">
+    <row r="22" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C22" s="3"/>
       <c r="D22" s="1">
         <v>0.20199478667791296</v>
@@ -13264,7 +12941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:57">
+    <row r="23" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="D23" s="1">
         <v>0.55620523524281973</v>
@@ -13443,7 +13120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:57">
+    <row r="24" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C24" s="3"/>
       <c r="D24" s="1">
         <v>0.20291450437699848</v>
@@ -13622,7 +13299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:57">
+    <row r="25" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C25" s="3"/>
       <c r="D25" s="1">
         <v>0.32801993833602577</v>
@@ -13801,7 +13478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:57">
+    <row r="26" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C26" s="3"/>
       <c r="D26" s="1">
         <v>0.25796413577511235</v>
@@ -13980,7 +13657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:57">
+    <row r="27" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
       <c r="D27" s="1">
         <v>1</v>
@@ -14159,7 +13836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:57">
+    <row r="28" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="D28" s="1">
         <v>0.33782708354181856</v>
@@ -14338,7 +14015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:57">
+    <row r="29" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C29" s="3"/>
       <c r="D29" s="1">
         <v>0.16907556457800207</v>
@@ -14517,7 +14194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:57">
+    <row r="30" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
       <c r="D30" s="1">
         <v>0.27950363836509456</v>
@@ -14696,7 +14373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:57">
+    <row r="31" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
       <c r="D31" s="1">
         <v>0.3910134526583654</v>
@@ -14875,7 +14552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:57">
+    <row r="32" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
       <c r="D32" s="1">
         <v>0.37633609248643057</v>
@@ -15054,7 +14731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="3:57">
+    <row r="33" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C33" s="3"/>
       <c r="D33" s="1">
         <v>0.30860579374496655</v>
@@ -15233,7 +14910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:57">
+    <row r="34" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C34" s="3"/>
       <c r="D34" s="1">
         <v>0</v>
@@ -15412,7 +15089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:57">
+    <row r="35" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C35" s="3"/>
       <c r="D35" s="1">
         <v>0.60799534899236107</v>
@@ -15591,7 +15268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:57">
+    <row r="36" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C36" s="3"/>
       <c r="D36" s="1">
         <v>0.76604859731137442</v>
@@ -15770,7 +15447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="3:57">
+    <row r="37" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
       <c r="D37" s="1">
         <v>0.41586489204039134</v>
@@ -15949,7 +15626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:57">
+    <row r="38" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C38" s="3"/>
       <c r="D38" s="1">
         <v>0.24080877972999376</v>
@@ -16128,7 +15805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:57">
+    <row r="39" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C39" s="3"/>
       <c r="D39" s="1">
         <v>0.37862347329244639</v>
@@ -16307,7 +15984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:57">
+    <row r="40" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C40" s="3"/>
       <c r="D40" s="1">
         <v>0.37112753577606544</v>
@@ -16486,7 +16163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:57">
+    <row r="41" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C41" s="3"/>
       <c r="D41" s="1">
         <v>0.4234180140769227</v>
@@ -16665,7 +16342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:57">
+    <row r="42" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
       <c r="D42" s="1">
         <v>0.15293523376555299</v>
@@ -16780,11 +16457,11 @@
         <v>0.78115837587822112</v>
       </c>
       <c r="Y42">
-        <f t="shared" ref="Y42:Y73" si="39">MIN(W42:X42)</f>
+        <f t="shared" ref="Y42:Y60" si="39">MIN(W42:X42)</f>
         <v>0.77196367085123285</v>
       </c>
       <c r="Z42">
-        <f t="shared" ref="Z42:Z73" si="40">IF(Y42 =W42,1,0)</f>
+        <f t="shared" ref="Z42:Z60" si="40">IF(Y42 =W42,1,0)</f>
         <v>1</v>
       </c>
       <c r="AA42">
@@ -16824,11 +16501,11 @@
         <v>0.68074032065418388</v>
       </c>
       <c r="AE42">
-        <f t="shared" ref="AE42:AE73" si="44">MIN(AC42:AD42)</f>
+        <f t="shared" ref="AE42:AE60" si="44">MIN(AC42:AD42)</f>
         <v>0.68074032065418388</v>
       </c>
       <c r="AF42">
-        <f t="shared" ref="AF42:AF73" si="45">IF(AE42 =AC42,1,0)</f>
+        <f t="shared" ref="AF42:AF60" si="45">IF(AE42 =AC42,1,0)</f>
         <v>0</v>
       </c>
       <c r="AG42">
@@ -16940,7 +16617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:57">
+    <row r="43" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C43" s="3"/>
       <c r="D43" s="1">
         <v>0.70857815456022721</v>
@@ -17119,7 +16796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="3:57">
+    <row r="44" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C44" s="3"/>
       <c r="D44" s="1">
         <v>0.68862552240441843</v>
@@ -17298,7 +16975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:57">
+    <row r="45" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C45" s="3"/>
       <c r="D45" s="1">
         <v>0.18749851081978774</v>
@@ -17477,7 +17154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:57">
+    <row r="46" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C46" s="3"/>
       <c r="D46" s="1">
         <v>0.12904640047272536</v>
@@ -17656,7 +17333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:57">
+    <row r="47" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
       <c r="D47" s="1">
         <v>6.340810209342998E-2</v>
@@ -17835,7 +17512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:57">
+    <row r="48" spans="3:57" x14ac:dyDescent="0.3">
       <c r="C48" s="3"/>
       <c r="D48" s="1">
         <v>0.68265450542538131</v>
@@ -18014,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:57">
+    <row r="49" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C49" s="3"/>
       <c r="D49" s="1">
         <v>0.30225831200827269</v>
@@ -18193,7 +17870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:57">
+    <row r="50" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C50" s="3"/>
       <c r="D50" s="1">
         <v>4.0472344136442268E-2</v>
@@ -18372,7 +18049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:57">
+    <row r="51" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C51" s="3"/>
       <c r="D51" s="1">
         <v>0.3155203553064852</v>
@@ -18551,7 +18228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:57">
+    <row r="52" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
       <c r="D52" s="1">
         <v>0.32766730046176501</v>
@@ -18730,7 +18407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:57">
+    <row r="53" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C53" s="3"/>
       <c r="D53" s="1">
         <v>0.7953699600184897</v>
@@ -18909,7 +18586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:57">
+    <row r="54" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C54" s="3"/>
       <c r="D54" s="1">
         <v>0.27257954605021756</v>
@@ -19088,7 +18765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:57">
+    <row r="55" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C55" s="3"/>
       <c r="D55" s="1">
         <v>0.96349244926065181</v>
@@ -19267,7 +18944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:57">
+    <row r="56" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C56" s="3"/>
       <c r="D56" s="1">
         <v>7.7832897301367193E-2</v>
@@ -19446,7 +19123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:57">
+    <row r="57" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
       <c r="D57" s="1">
         <v>0.97002578068783452</v>
@@ -19625,7 +19302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:57">
+    <row r="58" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C58" s="3"/>
       <c r="D58" s="1">
         <v>0.49699543000376467</v>
@@ -19804,7 +19481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:57">
+    <row r="59" spans="2:57" x14ac:dyDescent="0.3">
       <c r="C59" s="3"/>
       <c r="D59" s="1">
         <v>0.30401197062621815</v>
@@ -19983,7 +19660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:57" ht="14.4" thickBot="1">
+    <row r="60" spans="2:57" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="5"/>
       <c r="D60" s="9">
         <v>0.63525330359738286</v>
@@ -20162,7 +19839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:57">
+    <row r="61" spans="2:57" x14ac:dyDescent="0.3">
       <c r="S61" s="35">
         <f>SUM(S10:S60)</f>
         <v>45.242113445470736</v>
@@ -20223,7 +19900,7 @@
         <f>SUM(AS10:AS60)</f>
         <v>18</v>
       </c>
-      <c r="AW61" s="40">
+      <c r="AW61" s="37">
         <f>SUM(AW10:AW60)</f>
         <v>37.23441775115306</v>
       </c>
@@ -20235,7 +19912,7 @@
         <f>SUM(AY10:AY60)</f>
         <v>19</v>
       </c>
-      <c r="BC61" s="40">
+      <c r="BC61" s="37">
         <f>SUM(BC10:BC60)</f>
         <v>37.22275832023994</v>
       </c>
@@ -20248,7 +19925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="2:57">
+    <row r="62" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>30</v>
       </c>
@@ -20304,7 +19981,7 @@
         <v>0.43933721409926629</v>
       </c>
     </row>
-    <row r="63" spans="2:57">
+    <row r="63" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>31</v>
       </c>
@@ -20360,7 +20037,12 @@
         <v>0.68289816816738602</v>
       </c>
     </row>
-    <row r="66" spans="2:15">
+    <row r="64" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="S64" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>30</v>
       </c>
@@ -20416,7 +20098,7 @@
         <v>0.42018842992429167</v>
       </c>
     </row>
-    <row r="67" spans="2:15">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>31</v>
       </c>
@@ -20472,7 +20154,7 @@
         <v>0.69532746166677761</v>
       </c>
     </row>
-    <row r="70" spans="2:15">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>30</v>
       </c>
@@ -20528,7 +20210,7 @@
         <v>0.38395351967143371</v>
       </c>
     </row>
-    <row r="71" spans="2:15">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>31</v>
       </c>
@@ -20584,7 +20266,7 @@
         <v>0.7221613296009608</v>
       </c>
     </row>
-    <row r="74" spans="2:15">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>30</v>
       </c>
@@ -20640,7 +20322,7 @@
         <v>0.37236155459371811</v>
       </c>
     </row>
-    <row r="75" spans="2:15">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>31</v>
       </c>
@@ -20696,7 +20378,7 @@
         <v>0.68516039027383424</v>
       </c>
     </row>
-    <row r="78" spans="2:15">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>30</v>
       </c>
@@ -20752,7 +20434,7 @@
         <v>0.37413571800337003</v>
       </c>
     </row>
-    <row r="79" spans="2:15">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>31</v>
       </c>
@@ -20808,7 +20490,7 @@
         <v>0.5921451366048297</v>
       </c>
     </row>
-    <row r="82" spans="2:15">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>30</v>
       </c>
@@ -20864,7 +20546,7 @@
         <v>0.37227099197976271</v>
       </c>
     </row>
-    <row r="83" spans="2:15">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>31</v>
       </c>
@@ -20922,106 +20604,58 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="T10:U61">
-    <cfRule type="cellIs" dxfId="53" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="33" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="34" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z10:Z61">
-    <cfRule type="cellIs" dxfId="51" priority="29" operator="equal">
+  <conditionalFormatting sqref="Z10:AA61">
+    <cfRule type="cellIs" dxfId="11" priority="27" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="28" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA10:AA61">
-    <cfRule type="cellIs" dxfId="49" priority="27" operator="equal">
+  <conditionalFormatting sqref="AF10:AG61">
+    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF10:AF61">
-    <cfRule type="cellIs" dxfId="47" priority="25" operator="equal">
+  <conditionalFormatting sqref="AL10:AM61">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG10:AG61">
-    <cfRule type="cellIs" dxfId="45" priority="23" operator="equal">
+  <conditionalFormatting sqref="AR10:AS61">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL10:AL61">
-    <cfRule type="cellIs" dxfId="43" priority="19" operator="equal">
+  <conditionalFormatting sqref="AX10:AY61">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM10:AM61">
-    <cfRule type="cellIs" dxfId="41" priority="17" operator="equal">
+  <conditionalFormatting sqref="BD10:BE61">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="18" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR10:AR61">
-    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="16" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AS10:AS61">
-    <cfRule type="cellIs" dxfId="37" priority="13" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="14" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AX10:AX61">
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AY10:AY61">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BD10:BD61">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE10:BE61">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
+++ b/Minería de datos/Práctica 5/ca_cest_brandi_carlile (Editable).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Práctica 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D7704E-6641-4862-8821-3CF20A51E323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4DEB16-157C-4405-A6A2-3B872F6B348C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10212,9 +10212,9 @@
   <dimension ref="B5:BK87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="3:63" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
